--- a/devis-axione/Devis_BPU_Axione_RHD57.xlsx
+++ b/devis-axione/Devis_BPU_Axione_RHD57.xlsx
@@ -13,16 +13,15 @@
     <sheet name="Majorations" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Area" vbProcedure="false">BPU!$A$1:$J$117</definedName>
+    <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Area" vbProcedure="false">BPU!$A$1:$I$117</definedName>
     <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Titles" vbProcedure="false">BPU!$1:$1</definedName>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">BPU!$A$1:$L$117</definedName>
+    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">BPU!$A$1:$K$117</definedName>
     <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">Devis!$A$1:$H$61</definedName>
     <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Titles" vbProcedure="false">Devis!$14:$14</definedName>
-    <definedName function="false" hidden="false" name="Autoliq" vbProcedure="false">Devis!$N$4</definedName>
-    <definedName function="false" hidden="false" name="Grille" vbProcedure="false">Devis!$N$2</definedName>
+    <definedName function="false" hidden="false" name="Autoliq" vbProcedure="false">Devis!$N$3</definedName>
     <definedName function="false" hidden="false" name="ListeMajorations" vbProcedure="false">Majorations!$B$2:$B$3</definedName>
-    <definedName function="false" hidden="false" name="ListePrestations" vbProcedure="false">BPU!$K$2:$K$117</definedName>
-    <definedName function="false" hidden="false" name="TauxTVA" vbProcedure="false">Devis!$N$3</definedName>
+    <definedName function="false" hidden="false" name="ListePrestations" vbProcedure="false">BPU!$J$2:$J$117</definedName>
+    <definedName function="false" hidden="false" name="TauxTVA" vbProcedure="false">Devis!$N$2</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -39,20 +38,7 @@
     <author>Unknown Author</author>
   </authors>
   <commentList>
-    <comment ref="N2" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Prix BPU Axione : colonne « Prix unitaire » (Maintenance) et « Prix Cible V1 » (VDR Optique).
-Proposition Circet : colonne « Proposition Circet » des deux BPU.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="N4" authorId="0">
+    <comment ref="N3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -83,19 +69,7 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">Maintenance : colonne « Prix unitaire Euro(s) / u ».
-VDR Optique : colonne « Prix Cible V1 ».</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Colonne « Proposition Circet » des deux BPU.</t>
+VDR Optique : colonne « PU ».</t>
         </r>
       </text>
     </comment>
@@ -104,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1156" uniqueCount="588">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1148" uniqueCount="581">
   <si>
     <t xml:space="preserve">Raison sociale</t>
   </si>
@@ -124,10 +98,7 @@
     <t xml:space="preserve">DEV-2026-001</t>
   </si>
   <si>
-    <t xml:space="preserve">Grille de prix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prix BPU Axione</t>
+    <t xml:space="preserve">Taux de TVA</t>
   </si>
   <si>
     <t xml:space="preserve">Code postal – Ville</t>
@@ -136,7 +107,10 @@
     <t xml:space="preserve">Date</t>
   </si>
   <si>
-    <t xml:space="preserve">Taux de TVA</t>
+    <t xml:space="preserve">Autoliquidation TVA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Non</t>
   </si>
   <si>
     <t xml:space="preserve">SIRET : </t>
@@ -145,12 +119,6 @@
     <t xml:space="preserve">Validité (jours)</t>
   </si>
   <si>
-    <t xml:space="preserve">Autoliquidation TVA (sous-traitance BTP)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Non</t>
-  </si>
-  <si>
     <t xml:space="preserve">N° TVA intracommunautaire : </t>
   </si>
   <si>
@@ -187,7 +155,7 @@
     <t xml:space="preserve">Moselle Fibre – RHD57</t>
   </si>
   <si>
-    <t xml:space="preserve">• Qté : en ml, U, BPE, heures, fibres… selon l'unité affichée.</t>
+    <t xml:space="preserve">• Qté : en ml, unités, heures, fibres… selon l'unité affichée.</t>
   </si>
   <si>
     <t xml:space="preserve">Contact</t>
@@ -211,10 +179,13 @@
     <t xml:space="preserve">Base de prix</t>
   </si>
   <si>
-    <t xml:space="preserve">• Grille de prix : Prix BPU Axione ou Proposition Circet. Tout le devis bascule d'un coup.</t>
+    <t xml:space="preserve">BPU Moselle Fibre – RHD57 (Maintenance et VDR Optique)</t>
   </si>
   <si>
     <t xml:space="preserve">• Les 6 lignes remplies sont un exemple : effacer les colonnes Prestation, Qté et Majoration.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• 30 lignes prévues. Pour en ajouter : insérer des lignes au milieu du tableau, puis recopier une ligne remplie vers le bas.</t>
   </si>
   <si>
     <t xml:space="preserve">N°</t>
@@ -248,15 +219,12 @@
     <t xml:space="preserve">prix</t>
   </si>
   <si>
-    <t xml:space="preserve">• 30 lignes prévues. Pour en ajouter : insérer des lignes au milieu du tableau, puis recopier une ligne remplie vers le bas.</t>
+    <t xml:space="preserve">• Seules les colonnes A à H s'impriment (paysage, une page de large).</t>
   </si>
   <si>
     <t xml:space="preserve">RA-F1 · Raccordement abonné Opera Pro (PM)</t>
   </si>
   <si>
-    <t xml:space="preserve">• Seules les colonnes A à H s'impriment (paysage, une page de large).</t>
-  </si>
-  <si>
     <t xml:space="preserve">MC-01 · Intervention Immédiate en HO TELECOM - opérations sur equipement actif</t>
   </si>
   <si>
@@ -287,7 +255,7 @@
     <t xml:space="preserve">Prix unitaires HT issus du BPU Moselle Fibre – RHD57 (Maintenance et VDR Optique).</t>
   </si>
   <si>
-    <t xml:space="preserve">Hors fourniture, sauf mention contraire du BPU. Travaux en hauteur nécessitant une nacelle non compris dans les forfaits de raccordement.</t>
+    <t xml:space="preserve">Hors fourniture, sauf mention contraire du BPU.</t>
   </si>
   <si>
     <t xml:space="preserve">Conditions de paiement : à préciser.</t>
@@ -317,14 +285,10 @@
     <t xml:space="preserve">Descriptif</t>
   </si>
   <si>
-    <t xml:space="preserve">Prix BPU Axione
+    <t xml:space="preserve">Prix BPU
 € HT / u</t>
   </si>
   <si>
-    <t xml:space="preserve">Proposition Circet
-€ HT / u</t>
-  </si>
-  <si>
     <t xml:space="preserve">Commentaire</t>
   </si>
   <si>
@@ -349,16 +313,16 @@
     <t xml:space="preserve">Raccordement abonné Opera Pro (PM)</t>
   </si>
   <si>
-    <t xml:space="preserve">Aiguillage, Tirage , Racco et mise en service quelque soit la distance et le type de raccordement ( Souterrain , Aérien,Façade, Immeuble) Hors founiture</t>
+    <t xml:space="preserve">Aiguillage, Tirage , Racco et mise en service quelque soit la distance et le type de raccordement ( Souterrain , Aérien,Façade, Immeuble)</t>
   </si>
   <si>
     <t xml:space="preserve">Forfait par opération</t>
   </si>
   <si>
-    <t xml:space="preserve">à l'acte / Hors travaux en hauteur (aerien ou façade) nécessitant nacelle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maintenance BPU ST Circet · BPU ligne 4</t>
+    <t xml:space="preserve">à l'acte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maintenance BPU ST · BPU ligne 4</t>
   </si>
   <si>
     <t xml:space="preserve">RA-F2</t>
@@ -370,7 +334,7 @@
     <t xml:space="preserve">RA-F2 · Raccordement abonné Opera Office (PM)</t>
   </si>
   <si>
-    <t xml:space="preserve">Maintenance BPU ST Circet · BPU ligne 5</t>
+    <t xml:space="preserve">Maintenance BPU ST · BPU ligne 5</t>
   </si>
   <si>
     <t xml:space="preserve">RA-F3</t>
@@ -382,7 +346,7 @@
     <t xml:space="preserve">RA-F3 · Raccordement abonné Opera Business BLOM (PM)</t>
   </si>
   <si>
-    <t xml:space="preserve">Maintenance BPU ST Circet · BPU ligne 6</t>
+    <t xml:space="preserve">Maintenance BPU ST · BPU ligne 6</t>
   </si>
   <si>
     <t xml:space="preserve">RA-F4</t>
@@ -394,7 +358,7 @@
     <t xml:space="preserve">RA-F4 · Raccordement abonné Opera Business BLOM (NRO)</t>
   </si>
   <si>
-    <t xml:space="preserve">Maintenance BPU ST Circet · BPU ligne 7</t>
+    <t xml:space="preserve">Maintenance BPU ST · BPU ligne 7</t>
   </si>
   <si>
     <t xml:space="preserve">RA-ON</t>
@@ -406,13 +370,10 @@
     <t xml:space="preserve">Pré-visite : reportage photos + aiguillage de la partie privée uniquement + CRVT : 108,45€ / MES : Aiguillage de la partie publique / Tirage et Raccordement + pose des équipements (PTO + ADVA) chez le client Aiguillage Hors founiture : 351,06€ / Jusqu'à 300ml ( 0,93€/ml au dela)</t>
   </si>
   <si>
-    <t xml:space="preserve">à l'acte / ok</t>
-  </si>
-  <si>
     <t xml:space="preserve">RA-ON · Raccordement abonné Opera Business BLOD</t>
   </si>
   <si>
-    <t xml:space="preserve">Maintenance BPU ST Circet · BPU ligne 8</t>
+    <t xml:space="preserve">Maintenance BPU ST · BPU ligne 8</t>
   </si>
   <si>
     <t xml:space="preserve">Raccordement abonné Opera Business BLOD – ml au-delà de 300 ml</t>
@@ -436,13 +397,10 @@
     <t xml:space="preserve">Raccordement Service à destination des personnes âgées en situation de dépendance (BLOM)</t>
   </si>
   <si>
-    <t xml:space="preserve">Aiguillage, Tirage , Racco et mise en service quelque soit la distance et le type de raccordement ( Souterrain , Aérien,Façade, Immeuble)</t>
-  </si>
-  <si>
     <t xml:space="preserve">RA-B1 · Raccordement Service à destination des personnes âgées en situation de dépendance (BLOM)</t>
   </si>
   <si>
-    <t xml:space="preserve">Maintenance BPU ST Circet · BPU ligne 9</t>
+    <t xml:space="preserve">Maintenance BPU ST · BPU ligne 9</t>
   </si>
   <si>
     <t xml:space="preserve">Churn Opéra Pro</t>
@@ -451,13 +409,10 @@
     <t xml:space="preserve">Mise en place d'une Jarretierage au POP/NRO/PM + Pose ONT/PTO chez le client pour MES</t>
   </si>
   <si>
-    <t xml:space="preserve">à l'acte</t>
-  </si>
-  <si>
     <t xml:space="preserve">RA-ON · Churn Opéra Pro</t>
   </si>
   <si>
-    <t xml:space="preserve">Maintenance BPU ST Circet · BPU ligne 10</t>
+    <t xml:space="preserve">Maintenance BPU ST · BPU ligne 10</t>
   </si>
   <si>
     <t xml:space="preserve">Churn Opéra Office</t>
@@ -466,7 +421,7 @@
     <t xml:space="preserve">RA-B1 · Churn Opéra Office</t>
   </si>
   <si>
-    <t xml:space="preserve">Maintenance BPU ST Circet · BPU ligne 11</t>
+    <t xml:space="preserve">Maintenance BPU ST · BPU ligne 11</t>
   </si>
   <si>
     <t xml:space="preserve">RA-B2</t>
@@ -478,7 +433,7 @@
     <t xml:space="preserve">RA-B2 · Churn Opéra Business</t>
   </si>
   <si>
-    <t xml:space="preserve">Maintenance BPU ST Circet · BPU ligne 12</t>
+    <t xml:space="preserve">Maintenance BPU ST · BPU ligne 12</t>
   </si>
   <si>
     <t xml:space="preserve">RA-RO</t>
@@ -493,7 +448,7 @@
     <t xml:space="preserve">RA-RO · Raccordement abonné FttO - Zone 0 (BLOD)</t>
   </si>
   <si>
-    <t xml:space="preserve">Maintenance BPU ST Circet · BPU ligne 13</t>
+    <t xml:space="preserve">Maintenance BPU ST · BPU ligne 13</t>
   </si>
   <si>
     <t xml:space="preserve">Raccordement abonné FttO - Zone 1 (BLOD)</t>
@@ -502,7 +457,7 @@
     <t xml:space="preserve">RA-RO · Raccordement abonné FttO - Zone 1 (BLOD)</t>
   </si>
   <si>
-    <t xml:space="preserve">Maintenance BPU ST Circet · BPU ligne 14</t>
+    <t xml:space="preserve">Maintenance BPU ST · BPU ligne 14</t>
   </si>
   <si>
     <t xml:space="preserve">Raccordement abonné FttO - Zone 2 (BLOD)</t>
@@ -511,7 +466,7 @@
     <t xml:space="preserve">RA-RO · Raccordement abonné FttO - Zone 2 (BLOD)</t>
   </si>
   <si>
-    <t xml:space="preserve">Maintenance BPU ST Circet · BPU ligne 15</t>
+    <t xml:space="preserve">Maintenance BPU ST · BPU ligne 15</t>
   </si>
   <si>
     <t xml:space="preserve">Rémunération et conditions de paiement au titre des prestations de maintenance</t>
@@ -529,13 +484,13 @@
     <t xml:space="preserve">Forfait global Mensuel</t>
   </si>
   <si>
-    <t xml:space="preserve">Forfait mensuel / Binome en astreinte</t>
+    <t xml:space="preserve">Forfait mensuel</t>
   </si>
   <si>
     <t xml:space="preserve">AS-01 · Forfait mensuel pour mise à disposition d'une astreinte d'un technicien équipé</t>
   </si>
   <si>
-    <t xml:space="preserve">Maintenance BPU ST Circet · BPU ligne 18</t>
+    <t xml:space="preserve">Maintenance BPU ST · BPU ligne 18</t>
   </si>
   <si>
     <t xml:space="preserve">AS-02</t>
@@ -547,7 +502,7 @@
     <t xml:space="preserve">AS-02 · Forfait mensuel pour mise à disposition d'un 2 ème technicien d'astreinte équipé</t>
   </si>
   <si>
-    <t xml:space="preserve">Maintenance BPU ST Circet · BPU ligne 19</t>
+    <t xml:space="preserve">Maintenance BPU ST · BPU ligne 19</t>
   </si>
   <si>
     <t xml:space="preserve">Mini-forfait curatif</t>
@@ -562,7 +517,7 @@
     <t xml:space="preserve">Forfait par intervention</t>
   </si>
   <si>
-    <t xml:space="preserve">Maintenance BPU ST Circet · BPU ligne 22</t>
+    <t xml:space="preserve">Maintenance BPU ST · BPU ligne 22</t>
   </si>
   <si>
     <t xml:space="preserve">MC-02</t>
@@ -574,7 +529,7 @@
     <t xml:space="preserve">MC-02 · Intervention Programmée en HO TELECOM - opérations sur equipement actif</t>
   </si>
   <si>
-    <t xml:space="preserve">Maintenance BPU ST Circet · BPU ligne 23</t>
+    <t xml:space="preserve">Maintenance BPU ST · BPU ligne 23</t>
   </si>
   <si>
     <t xml:space="preserve">MC-03</t>
@@ -586,7 +541,7 @@
     <t xml:space="preserve">MC-03 · Intervention Immédiate en HO ENVIRONNEMENT - énergie, climatisation, contrôle d'accès</t>
   </si>
   <si>
-    <t xml:space="preserve">Maintenance BPU ST Circet · BPU ligne 24</t>
+    <t xml:space="preserve">Maintenance BPU ST · BPU ligne 24</t>
   </si>
   <si>
     <t xml:space="preserve">MC-04</t>
@@ -598,7 +553,7 @@
     <t xml:space="preserve">MC-04 · Intervention Programmée en HO ENVIRONNEMENT - énergie, climatisation, contrôle d'accès</t>
   </si>
   <si>
-    <t xml:space="preserve">Maintenance BPU ST Circet · BPU ligne 25</t>
+    <t xml:space="preserve">Maintenance BPU ST · BPU ligne 25</t>
   </si>
   <si>
     <t xml:space="preserve">MC-05</t>
@@ -610,7 +565,7 @@
     <t xml:space="preserve">MC-05 · SAV et ticket à froid yc. Intervention d'un technicien en HO</t>
   </si>
   <si>
-    <t xml:space="preserve">Maintenance BPU ST Circet · BPU ligne 26</t>
+    <t xml:space="preserve">Maintenance BPU ST · BPU ligne 26</t>
   </si>
   <si>
     <t xml:space="preserve">MC-06</t>
@@ -622,7 +577,7 @@
     <t xml:space="preserve">MC-06 · SAV et ticket à froid yc. Intervention de deux techniciens (nacelle incluse) en HO</t>
   </si>
   <si>
-    <t xml:space="preserve">Maintenance BPU ST Circet · BPU ligne 27</t>
+    <t xml:space="preserve">Maintenance BPU ST · BPU ligne 27</t>
   </si>
   <si>
     <t xml:space="preserve">MC-09</t>
@@ -634,7 +589,7 @@
     <t xml:space="preserve">MC-09 · SAV GTR 10h : Intervention d'un technicien en HO</t>
   </si>
   <si>
-    <t xml:space="preserve">Maintenance BPU ST Circet · BPU ligne 30</t>
+    <t xml:space="preserve">Maintenance BPU ST · BPU ligne 30</t>
   </si>
   <si>
     <t xml:space="preserve">MC-10</t>
@@ -646,7 +601,7 @@
     <t xml:space="preserve">MC-10 · SAV GTR 10h : Intervention de deux techniciens (nacelle incluse) en HO</t>
   </si>
   <si>
-    <t xml:space="preserve">Maintenance BPU ST Circet · BPU ligne 31</t>
+    <t xml:space="preserve">Maintenance BPU ST · BPU ligne 31</t>
   </si>
   <si>
     <t xml:space="preserve">Maintenance curative</t>
@@ -661,7 +616,7 @@
     <t xml:space="preserve">Forfait par heure</t>
   </si>
   <si>
-    <t xml:space="preserve">Maintenance BPU ST Circet · BPU ligne 33</t>
+    <t xml:space="preserve">Maintenance BPU ST · BPU ligne 33</t>
   </si>
   <si>
     <t xml:space="preserve">MC-T2</t>
@@ -673,7 +628,7 @@
     <t xml:space="preserve">MC-T2 · Heure de technicien équipé en HO (8h00 – 18h00) - Intervention Programmée</t>
   </si>
   <si>
-    <t xml:space="preserve">Maintenance BPU ST Circet · BPU ligne 34</t>
+    <t xml:space="preserve">Maintenance BPU ST · BPU ligne 34</t>
   </si>
   <si>
     <t xml:space="preserve">MC-T3</t>
@@ -685,7 +640,7 @@
     <t xml:space="preserve">MC-T3 · Heure de technicien équipé en HNO (18H01 – 7h59)</t>
   </si>
   <si>
-    <t xml:space="preserve">Maintenance BPU ST Circet · BPU ligne 35</t>
+    <t xml:space="preserve">Maintenance BPU ST · BPU ligne 35</t>
   </si>
   <si>
     <t xml:space="preserve">MC-T4</t>
@@ -697,7 +652,7 @@
     <t xml:space="preserve">MC-T4 · Intervention de 2 techniciens équipés d'une nacelle &lt;= 16m en HO</t>
   </si>
   <si>
-    <t xml:space="preserve">Maintenance BPU ST Circet · BPU ligne 36</t>
+    <t xml:space="preserve">Maintenance BPU ST · BPU ligne 36</t>
   </si>
   <si>
     <t xml:space="preserve">MC-T5</t>
@@ -709,7 +664,7 @@
     <t xml:space="preserve">MC-T5 · Intervention de 2 techniciens équipés d'une nacelle &lt;= 16m en HNO</t>
   </si>
   <si>
-    <t xml:space="preserve">Maintenance BPU ST Circet · BPU ligne 37</t>
+    <t xml:space="preserve">Maintenance BPU ST · BPU ligne 37</t>
   </si>
   <si>
     <t xml:space="preserve">MC-T6</t>
@@ -724,7 +679,7 @@
     <t xml:space="preserve">MC-T6 · Mise à disposition d'une nacelle exceptionnelle (&gt;16m, nacelle araignée, 4x4, inversée) - un…</t>
   </si>
   <si>
-    <t xml:space="preserve">Maintenance BPU ST Circet · BPU ligne 38</t>
+    <t xml:space="preserve">Maintenance BPU ST · BPU ligne 38</t>
   </si>
   <si>
     <t xml:space="preserve">Commandes des usagers</t>
@@ -742,7 +697,7 @@
     <t xml:space="preserve">PU-01 · Installation électrique au NRO yc. fourniture et pose du tiroir optique dans la baie de…</t>
   </si>
   <si>
-    <t xml:space="preserve">Maintenance BPU ST Circet · BPU ligne 40</t>
+    <t xml:space="preserve">Maintenance BPU ST · BPU ligne 40</t>
   </si>
   <si>
     <t xml:space="preserve">PU-02</t>
@@ -754,7 +709,7 @@
     <t xml:space="preserve">PU-02 · Fourniture et pose d'un tiroir optique dans la baie de transport</t>
   </si>
   <si>
-    <t xml:space="preserve">Maintenance BPU ST Circet · BPU ligne 41</t>
+    <t xml:space="preserve">Maintenance BPU ST · BPU ligne 41</t>
   </si>
   <si>
     <t xml:space="preserve">PU-03</t>
@@ -766,7 +721,7 @@
     <t xml:space="preserve">PU-03 · Fourniture et pose d’une jarretière entre la baie Opérateur et la baie OCEN</t>
   </si>
   <si>
-    <t xml:space="preserve">Maintenance BPU ST Circet · BPU ligne 42</t>
+    <t xml:space="preserve">Maintenance BPU ST · BPU ligne 42</t>
   </si>
   <si>
     <t xml:space="preserve">PU-04</t>
@@ -778,7 +733,7 @@
     <t xml:space="preserve">PU-04 · Fourniture et pose de jarretières entre la tête de câble OC et le tiroir transport PM dans le…</t>
   </si>
   <si>
-    <t xml:space="preserve">Maintenance BPU ST Circet · BPU ligne 43</t>
+    <t xml:space="preserve">Maintenance BPU ST · BPU ligne 43</t>
   </si>
   <si>
     <t xml:space="preserve">PU-05</t>
@@ -790,7 +745,7 @@
     <t xml:space="preserve">PU-05 · Fourniture et pose au NRO d'une baie 42U yc. raccordement du PDU</t>
   </si>
   <si>
-    <t xml:space="preserve">Maintenance BPU ST Circet · BPU ligne 44</t>
+    <t xml:space="preserve">Maintenance BPU ST · BPU ligne 44</t>
   </si>
   <si>
     <t xml:space="preserve">PU-06</t>
@@ -802,7 +757,7 @@
     <t xml:space="preserve">PU-06 · Fourniture et pose au NRO d'une baie 21U yc. raccordement du PDU</t>
   </si>
   <si>
-    <t xml:space="preserve">Maintenance BPU ST Circet · BPU ligne 45</t>
+    <t xml:space="preserve">Maintenance BPU ST · BPU ligne 45</t>
   </si>
   <si>
     <t xml:space="preserve">VDR Optique</t>
@@ -1009,9 +964,6 @@
     <t xml:space="preserve">Ce prix rémunère à l'unité la pose d'un Boitier de Protection d'Epissure comprenant : - la pose du BPE et sa fixation en chambre - les raccordements des fibres - la fourniture et la mise en place des signalisations chantier (déviations éventuelles, alternats manuels K10,...</t>
   </si>
   <si>
-    <t xml:space="preserve">BPE</t>
-  </si>
-  <si>
     <t xml:space="preserve">4.3.1 · Pose boitier pour protection d'épissure, capacité jusqu'à 12 épissures</t>
   </si>
   <si>
@@ -1264,9 +1216,6 @@
     <t xml:space="preserve">Pose de tiroir optique 19" 288 FO équipé des cassettes, des traversées et des pigtails fibre (connectique SC/APC), y compris de fixation et étiquetage.</t>
   </si>
   <si>
-    <t xml:space="preserve">Tiroir optique</t>
-  </si>
-  <si>
     <t xml:space="preserve">Hors Raccordement - Utilisation en plus de l'ARTICLE 4.8 - Raccordement fibre optique</t>
   </si>
   <si>
@@ -1432,7 +1381,7 @@
     <t xml:space="preserve">Ce prix rémunère à l'unité la pose d'un Point de Branchement Optique comprenant : - la pose du BPO en immeuble (en colonne montante ou en pied d'immeuble) - l'adduction de l'immeuble - les percements de colonne montante - le cheminement à l'intérieur de l immeuble</t>
   </si>
   <si>
-    <t xml:space="preserve">PBO</t>
+    <t xml:space="preserve">Forfait</t>
   </si>
   <si>
     <t xml:space="preserve">4.6.1 · installation du réseau de distribution vertical (immeuble de 4 à 12 locaux), y compris la…</t>
@@ -1489,7 +1438,10 @@
     <t xml:space="preserve">Mesures réflectométriques de fibre otpique dans les deux sens aux longueurs d’onde 1310 nm et 1550 nm</t>
   </si>
   <si>
-    <t xml:space="preserve">fibre</t>
+    <t xml:space="preserve">u (à la fibre)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">à la fibre</t>
   </si>
   <si>
     <t xml:space="preserve">4.7.1 · Mesures réflectométriques de fibre otpique dans les deux sens aux longueurs d’onde 1310 nm et…</t>
@@ -1855,22 +1807,22 @@
     <t xml:space="preserve">coef. appliqué au forfait</t>
   </si>
   <si>
-    <t xml:space="preserve">Majoration par technicien supplémentaire sur une intervention (à l'acte / Coeff en pourcentage?)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maintenance BPU ST Circet · BPU ligne 28</t>
+    <t xml:space="preserve">Majoration par technicien supplémentaire sur une intervention (à l'acte)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maintenance BPU ST · BPU ligne 28</t>
   </si>
   <si>
     <t xml:space="preserve">MC-08</t>
   </si>
   <si>
-    <t xml:space="preserve">Majoration en cas d'intervention en HNO (min 20% de l'inter. en HNO) (à l'acte / Coeff en pourcentage?)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maintenance BPU ST Circet · BPU ligne 29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Le montant de la ligne du devis est multiplié par le coefficient (ex. 1,4078 = +40,78 %). La Proposition Circet ne donne pas de coefficient : celui du BPU s'applique dans les deux grilles.</t>
+    <t xml:space="preserve">Majoration en cas d'intervention en HNO (min 20% de l'inter. en HNO) (à l'acte)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maintenance BPU ST · BPU ligne 29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le montant de la ligne du devis est multiplié par le coefficient (ex. 1,4078 = +40,78 %).</t>
   </si>
 </sst>
 </file>
@@ -1879,8 +1831,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="6">
     <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
-    <numFmt numFmtId="166" formatCode="0%"/>
+    <numFmt numFmtId="165" formatCode="0%"/>
+    <numFmt numFmtId="166" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="167" formatCode="General"/>
     <numFmt numFmtId="168" formatCode="_-* #,##0.00&quot; €&quot;_-;\-* #,##0.00&quot; €&quot;_-;_-* \-??&quot; €&quot;_-;_-@_-"/>
     <numFmt numFmtId="169" formatCode="0.0000"/>
@@ -2099,23 +2051,23 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2589,30 +2541,30 @@
       <c r="L2" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="N2" s="8" t="s">
-        <v>7</v>
+      <c r="N2" s="8" t="n">
+        <v>0.2</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3" s="4"/>
       <c r="F3" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G3" s="5"/>
       <c r="H3" s="9" t="n">
         <v>46316</v>
       </c>
       <c r="L3" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="N3" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="N3" s="10" t="n">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
         <v>11</v>
       </c>
@@ -2624,20 +2576,14 @@
       <c r="H4" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="L4" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="N4" s="8" t="s">
-        <v>14</v>
-      </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B5" s="4"/>
       <c r="F5" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G5" s="5"/>
       <c r="H5" s="11" t="n">
@@ -2647,32 +2593,32 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B6" s="4"/>
       <c r="F6" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G6" s="5"/>
       <c r="H6" s="6"/>
       <c r="L6" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="M6" s="3"/>
       <c r="N6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L7" s="12" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B8" s="13"/>
       <c r="C8" s="13" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D8" s="13"/>
       <c r="E8" s="13"/>
@@ -2680,122 +2626,121 @@
       <c r="G8" s="13"/>
       <c r="H8" s="13"/>
       <c r="L8" s="12" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" s="10"/>
+      <c r="C9" s="14" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="8" t="s">
+      <c r="D9" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="8"/>
-      <c r="C9" s="14" t="s">
+      <c r="E9" s="10"/>
+      <c r="F9" s="10"/>
+      <c r="G9" s="10"/>
+      <c r="H9" s="10"/>
+      <c r="L9" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="D9" s="8" t="s">
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="8"/>
-      <c r="L9" s="12" t="s">
+      <c r="B10" s="10"/>
+      <c r="C10" s="14" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="8" t="s">
+      <c r="D10" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="B10" s="8"/>
-      <c r="C10" s="14" t="s">
+      <c r="E10" s="10"/>
+      <c r="F10" s="10"/>
+      <c r="G10" s="10"/>
+      <c r="H10" s="10"/>
+      <c r="L10" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="D10" s="8" t="s">
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" s="10"/>
+      <c r="C11" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="8"/>
-      <c r="L10" s="12" t="s">
+      <c r="D11" s="10"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="10"/>
+      <c r="G11" s="10"/>
+      <c r="H11" s="10"/>
+      <c r="L11" s="12" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" s="8"/>
-      <c r="C11" s="14" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12" s="10"/>
+      <c r="C12" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
-      <c r="G11" s="8"/>
-      <c r="H11" s="8"/>
-      <c r="L11" s="12" t="s">
+      <c r="D12" s="15" t="s">
         <v>33</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B12" s="8"/>
-      <c r="C12" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="D12" s="15" t="str">
-        <f aca="false">"BPU Moselle Fibre RHD57 – "&amp;Grille</f>
-        <v>BPU Moselle Fibre RHD57 – Prix BPU Axione</v>
       </c>
       <c r="E12" s="15"/>
       <c r="F12" s="15"/>
       <c r="G12" s="15"/>
       <c r="H12" s="15"/>
       <c r="L12" s="12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L13" s="12" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="B14" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="16" t="s">
+      <c r="C14" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="C14" s="16" t="s">
+      <c r="D14" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="D14" s="16" t="s">
+      <c r="E14" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="E14" s="16" t="s">
+      <c r="F14" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="F14" s="16" t="s">
+      <c r="G14" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="G14" s="16" t="s">
+      <c r="H14" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="H14" s="16" t="s">
+      <c r="J14" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="J14" s="17" t="s">
+      <c r="K14" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="K14" s="17" t="s">
+      <c r="L14" s="12" t="s">
         <v>46</v>
-      </c>
-      <c r="L14" s="12" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2804,7 +2749,7 @@
         <v>1</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C15" s="18" t="str">
         <f aca="false">IF(OR($J15="",$J15=0),"",INDEX(BPU!$G$2:$G$117,$J15)&amp;"")</f>
@@ -2818,7 +2763,7 @@
         <v>210</v>
       </c>
       <c r="F15" s="21"/>
-      <c r="G15" s="8"/>
+      <c r="G15" s="10"/>
       <c r="H15" s="22" t="n">
         <f aca="false">IF($B15="","",IF(AND($F15="",NOT(ISNUMBER($E15))),"PU à saisir",ROUND(N($D15)*IF($F15&lt;&gt;"",$F15,$E15)*IF($G15="",1,IFERROR(INDEX(Majorations!$C$2:$C$3,MATCH($G15,ListeMajorations,0)),1)),2)))</f>
         <v>420</v>
@@ -2828,11 +2773,8 @@
         <v>1</v>
       </c>
       <c r="K15" s="23" t="n">
-        <f aca="false">IF(OR($J15="",$J15=0),"",IF(Grille="Proposition Circet",INDEX(BPU!$I$2:$I$117,$J15),INDEX(BPU!$H$2:$H$117,$J15)))</f>
+        <f aca="false">IF(OR($J15="",$J15=0),"",INDEX(BPU!$H$2:$H$117,$J15))</f>
         <v>210</v>
-      </c>
-      <c r="L15" s="12" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2841,7 +2783,7 @@
         <v>2</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C16" s="18" t="str">
         <f aca="false">IF(OR($J16="",$J16=0),"",INDEX(BPU!$G$2:$G$117,$J16)&amp;"")</f>
@@ -2855,8 +2797,8 @@
         <v>160.34</v>
       </c>
       <c r="F16" s="21"/>
-      <c r="G16" s="8" t="s">
-        <v>51</v>
+      <c r="G16" s="10" t="s">
+        <v>49</v>
       </c>
       <c r="H16" s="22" t="n">
         <f aca="false">IF($B16="","",IF(AND($F16="",NOT(ISNUMBER($E16))),"PU à saisir",ROUND(N($D16)*IF($F16&lt;&gt;"",$F16,$E16)*IF($G16="",1,IFERROR(INDEX(Majorations!$C$2:$C$3,MATCH($G16,ListeMajorations,0)),1)),2)))</f>
@@ -2867,7 +2809,7 @@
         <v>16</v>
       </c>
       <c r="K16" s="23" t="n">
-        <f aca="false">IF(OR($J16="",$J16=0),"",IF(Grille="Proposition Circet",INDEX(BPU!$I$2:$I$117,$J16),INDEX(BPU!$H$2:$H$117,$J16)))</f>
+        <f aca="false">IF(OR($J16="",$J16=0),"",INDEX(BPU!$H$2:$H$117,$J16))</f>
         <v>160.341790896159</v>
       </c>
     </row>
@@ -2877,7 +2819,7 @@
         <v>3</v>
       </c>
       <c r="B17" s="19" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C17" s="18" t="str">
         <f aca="false">IF(OR($J17="",$J17=0),"",INDEX(BPU!$G$2:$G$117,$J17)&amp;"")</f>
@@ -2891,7 +2833,7 @@
         <v>35.93</v>
       </c>
       <c r="F17" s="21"/>
-      <c r="G17" s="8"/>
+      <c r="G17" s="10"/>
       <c r="H17" s="22" t="n">
         <f aca="false">IF($B17="","",IF(AND($F17="",NOT(ISNUMBER($E17))),"PU à saisir",ROUND(N($D17)*IF($F17&lt;&gt;"",$F17,$E17)*IF($G17="",1,IFERROR(INDEX(Majorations!$C$2:$C$3,MATCH($G17,ListeMajorations,0)),1)),2)))</f>
         <v>107.79</v>
@@ -2901,7 +2843,7 @@
         <v>24</v>
       </c>
       <c r="K17" s="23" t="n">
-        <f aca="false">IF(OR($J17="",$J17=0),"",IF(Grille="Proposition Circet",INDEX(BPU!$I$2:$I$117,$J17),INDEX(BPU!$H$2:$H$117,$J17)))</f>
+        <f aca="false">IF(OR($J17="",$J17=0),"",INDEX(BPU!$H$2:$H$117,$J17))</f>
         <v>35.92625</v>
       </c>
     </row>
@@ -2911,7 +2853,7 @@
         <v>4</v>
       </c>
       <c r="B18" s="19" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C18" s="18" t="str">
         <f aca="false">IF(OR($J18="",$J18=0),"",INDEX(BPU!$G$2:$G$117,$J18)&amp;"")</f>
@@ -2925,7 +2867,7 @@
         <v>1</v>
       </c>
       <c r="F18" s="21"/>
-      <c r="G18" s="8"/>
+      <c r="G18" s="10"/>
       <c r="H18" s="22" t="n">
         <f aca="false">IF($B18="","",IF(AND($F18="",NOT(ISNUMBER($E18))),"PU à saisir",ROUND(N($D18)*IF($F18&lt;&gt;"",$F18,$E18)*IF($G18="",1,IFERROR(INDEX(Majorations!$C$2:$C$3,MATCH($G18,ListeMajorations,0)),1)),2)))</f>
         <v>250</v>
@@ -2935,7 +2877,7 @@
         <v>40</v>
       </c>
       <c r="K18" s="23" t="n">
-        <f aca="false">IF(OR($J18="",$J18=0),"",IF(Grille="Proposition Circet",INDEX(BPU!$I$2:$I$117,$J18),INDEX(BPU!$H$2:$H$117,$J18)))</f>
+        <f aca="false">IF(OR($J18="",$J18=0),"",INDEX(BPU!$H$2:$H$117,$J18))</f>
         <v>1</v>
       </c>
     </row>
@@ -2945,11 +2887,11 @@
         <v>5</v>
       </c>
       <c r="B19" s="19" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C19" s="18" t="str">
         <f aca="false">IF(OR($J19="",$J19=0),"",INDEX(BPU!$G$2:$G$117,$J19)&amp;"")</f>
-        <v>BPE</v>
+        <v>u</v>
       </c>
       <c r="D19" s="6" t="n">
         <v>1</v>
@@ -2959,7 +2901,7 @@
         <v>130</v>
       </c>
       <c r="F19" s="21"/>
-      <c r="G19" s="8"/>
+      <c r="G19" s="10"/>
       <c r="H19" s="22" t="n">
         <f aca="false">IF($B19="","",IF(AND($F19="",NOT(ISNUMBER($E19))),"PU à saisir",ROUND(N($D19)*IF($F19&lt;&gt;"",$F19,$E19)*IF($G19="",1,IFERROR(INDEX(Majorations!$C$2:$C$3,MATCH($G19,ListeMajorations,0)),1)),2)))</f>
         <v>130</v>
@@ -2969,7 +2911,7 @@
         <v>51</v>
       </c>
       <c r="K19" s="23" t="n">
-        <f aca="false">IF(OR($J19="",$J19=0),"",IF(Grille="Proposition Circet",INDEX(BPU!$I$2:$I$117,$J19),INDEX(BPU!$H$2:$H$117,$J19)))</f>
+        <f aca="false">IF(OR($J19="",$J19=0),"",INDEX(BPU!$H$2:$H$117,$J19))</f>
         <v>130</v>
       </c>
     </row>
@@ -2979,11 +2921,11 @@
         <v>6</v>
       </c>
       <c r="B20" s="19" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C20" s="18" t="str">
         <f aca="false">IF(OR($J20="",$J20=0),"",INDEX(BPU!$G$2:$G$117,$J20)&amp;"")</f>
-        <v>fibre</v>
+        <v>u (à la fibre)</v>
       </c>
       <c r="D20" s="6" t="n">
         <v>24</v>
@@ -2993,7 +2935,7 @@
         <v>4.5</v>
       </c>
       <c r="F20" s="21"/>
-      <c r="G20" s="8"/>
+      <c r="G20" s="10"/>
       <c r="H20" s="22" t="n">
         <f aca="false">IF($B20="","",IF(AND($F20="",NOT(ISNUMBER($E20))),"PU à saisir",ROUND(N($D20)*IF($F20&lt;&gt;"",$F20,$E20)*IF($G20="",1,IFERROR(INDEX(Majorations!$C$2:$C$3,MATCH($G20,ListeMajorations,0)),1)),2)))</f>
         <v>108</v>
@@ -3003,7 +2945,7 @@
         <v>91</v>
       </c>
       <c r="K20" s="23" t="n">
-        <f aca="false">IF(OR($J20="",$J20=0),"",IF(Grille="Proposition Circet",INDEX(BPU!$I$2:$I$117,$J20),INDEX(BPU!$H$2:$H$117,$J20)))</f>
+        <f aca="false">IF(OR($J20="",$J20=0),"",INDEX(BPU!$H$2:$H$117,$J20))</f>
         <v>4.5</v>
       </c>
     </row>
@@ -3023,7 +2965,7 @@
         <v/>
       </c>
       <c r="F21" s="21"/>
-      <c r="G21" s="8"/>
+      <c r="G21" s="10"/>
       <c r="H21" s="22" t="str">
         <f aca="false">IF($B21="","",IF(AND($F21="",NOT(ISNUMBER($E21))),"PU à saisir",ROUND(N($D21)*IF($F21&lt;&gt;"",$F21,$E21)*IF($G21="",1,IFERROR(INDEX(Majorations!$C$2:$C$3,MATCH($G21,ListeMajorations,0)),1)),2)))</f>
         <v/>
@@ -3033,7 +2975,7 @@
         <v/>
       </c>
       <c r="K21" s="0" t="str">
-        <f aca="false">IF(OR($J21="",$J21=0),"",IF(Grille="Proposition Circet",INDEX(BPU!$I$2:$I$117,$J21),INDEX(BPU!$H$2:$H$117,$J21)))</f>
+        <f aca="false">IF(OR($J21="",$J21=0),"",INDEX(BPU!$H$2:$H$117,$J21))</f>
         <v/>
       </c>
     </row>
@@ -3053,7 +2995,7 @@
         <v/>
       </c>
       <c r="F22" s="21"/>
-      <c r="G22" s="8"/>
+      <c r="G22" s="10"/>
       <c r="H22" s="22" t="str">
         <f aca="false">IF($B22="","",IF(AND($F22="",NOT(ISNUMBER($E22))),"PU à saisir",ROUND(N($D22)*IF($F22&lt;&gt;"",$F22,$E22)*IF($G22="",1,IFERROR(INDEX(Majorations!$C$2:$C$3,MATCH($G22,ListeMajorations,0)),1)),2)))</f>
         <v/>
@@ -3063,7 +3005,7 @@
         <v/>
       </c>
       <c r="K22" s="0" t="str">
-        <f aca="false">IF(OR($J22="",$J22=0),"",IF(Grille="Proposition Circet",INDEX(BPU!$I$2:$I$117,$J22),INDEX(BPU!$H$2:$H$117,$J22)))</f>
+        <f aca="false">IF(OR($J22="",$J22=0),"",INDEX(BPU!$H$2:$H$117,$J22))</f>
         <v/>
       </c>
     </row>
@@ -3083,7 +3025,7 @@
         <v/>
       </c>
       <c r="F23" s="21"/>
-      <c r="G23" s="8"/>
+      <c r="G23" s="10"/>
       <c r="H23" s="22" t="str">
         <f aca="false">IF($B23="","",IF(AND($F23="",NOT(ISNUMBER($E23))),"PU à saisir",ROUND(N($D23)*IF($F23&lt;&gt;"",$F23,$E23)*IF($G23="",1,IFERROR(INDEX(Majorations!$C$2:$C$3,MATCH($G23,ListeMajorations,0)),1)),2)))</f>
         <v/>
@@ -3093,7 +3035,7 @@
         <v/>
       </c>
       <c r="K23" s="0" t="str">
-        <f aca="false">IF(OR($J23="",$J23=0),"",IF(Grille="Proposition Circet",INDEX(BPU!$I$2:$I$117,$J23),INDEX(BPU!$H$2:$H$117,$J23)))</f>
+        <f aca="false">IF(OR($J23="",$J23=0),"",INDEX(BPU!$H$2:$H$117,$J23))</f>
         <v/>
       </c>
     </row>
@@ -3113,7 +3055,7 @@
         <v/>
       </c>
       <c r="F24" s="21"/>
-      <c r="G24" s="8"/>
+      <c r="G24" s="10"/>
       <c r="H24" s="22" t="str">
         <f aca="false">IF($B24="","",IF(AND($F24="",NOT(ISNUMBER($E24))),"PU à saisir",ROUND(N($D24)*IF($F24&lt;&gt;"",$F24,$E24)*IF($G24="",1,IFERROR(INDEX(Majorations!$C$2:$C$3,MATCH($G24,ListeMajorations,0)),1)),2)))</f>
         <v/>
@@ -3123,7 +3065,7 @@
         <v/>
       </c>
       <c r="K24" s="0" t="str">
-        <f aca="false">IF(OR($J24="",$J24=0),"",IF(Grille="Proposition Circet",INDEX(BPU!$I$2:$I$117,$J24),INDEX(BPU!$H$2:$H$117,$J24)))</f>
+        <f aca="false">IF(OR($J24="",$J24=0),"",INDEX(BPU!$H$2:$H$117,$J24))</f>
         <v/>
       </c>
     </row>
@@ -3143,7 +3085,7 @@
         <v/>
       </c>
       <c r="F25" s="21"/>
-      <c r="G25" s="8"/>
+      <c r="G25" s="10"/>
       <c r="H25" s="22" t="str">
         <f aca="false">IF($B25="","",IF(AND($F25="",NOT(ISNUMBER($E25))),"PU à saisir",ROUND(N($D25)*IF($F25&lt;&gt;"",$F25,$E25)*IF($G25="",1,IFERROR(INDEX(Majorations!$C$2:$C$3,MATCH($G25,ListeMajorations,0)),1)),2)))</f>
         <v/>
@@ -3153,7 +3095,7 @@
         <v/>
       </c>
       <c r="K25" s="0" t="str">
-        <f aca="false">IF(OR($J25="",$J25=0),"",IF(Grille="Proposition Circet",INDEX(BPU!$I$2:$I$117,$J25),INDEX(BPU!$H$2:$H$117,$J25)))</f>
+        <f aca="false">IF(OR($J25="",$J25=0),"",INDEX(BPU!$H$2:$H$117,$J25))</f>
         <v/>
       </c>
     </row>
@@ -3173,7 +3115,7 @@
         <v/>
       </c>
       <c r="F26" s="21"/>
-      <c r="G26" s="8"/>
+      <c r="G26" s="10"/>
       <c r="H26" s="22" t="str">
         <f aca="false">IF($B26="","",IF(AND($F26="",NOT(ISNUMBER($E26))),"PU à saisir",ROUND(N($D26)*IF($F26&lt;&gt;"",$F26,$E26)*IF($G26="",1,IFERROR(INDEX(Majorations!$C$2:$C$3,MATCH($G26,ListeMajorations,0)),1)),2)))</f>
         <v/>
@@ -3183,7 +3125,7 @@
         <v/>
       </c>
       <c r="K26" s="0" t="str">
-        <f aca="false">IF(OR($J26="",$J26=0),"",IF(Grille="Proposition Circet",INDEX(BPU!$I$2:$I$117,$J26),INDEX(BPU!$H$2:$H$117,$J26)))</f>
+        <f aca="false">IF(OR($J26="",$J26=0),"",INDEX(BPU!$H$2:$H$117,$J26))</f>
         <v/>
       </c>
     </row>
@@ -3203,7 +3145,7 @@
         <v/>
       </c>
       <c r="F27" s="21"/>
-      <c r="G27" s="8"/>
+      <c r="G27" s="10"/>
       <c r="H27" s="22" t="str">
         <f aca="false">IF($B27="","",IF(AND($F27="",NOT(ISNUMBER($E27))),"PU à saisir",ROUND(N($D27)*IF($F27&lt;&gt;"",$F27,$E27)*IF($G27="",1,IFERROR(INDEX(Majorations!$C$2:$C$3,MATCH($G27,ListeMajorations,0)),1)),2)))</f>
         <v/>
@@ -3213,7 +3155,7 @@
         <v/>
       </c>
       <c r="K27" s="0" t="str">
-        <f aca="false">IF(OR($J27="",$J27=0),"",IF(Grille="Proposition Circet",INDEX(BPU!$I$2:$I$117,$J27),INDEX(BPU!$H$2:$H$117,$J27)))</f>
+        <f aca="false">IF(OR($J27="",$J27=0),"",INDEX(BPU!$H$2:$H$117,$J27))</f>
         <v/>
       </c>
     </row>
@@ -3233,7 +3175,7 @@
         <v/>
       </c>
       <c r="F28" s="21"/>
-      <c r="G28" s="8"/>
+      <c r="G28" s="10"/>
       <c r="H28" s="22" t="str">
         <f aca="false">IF($B28="","",IF(AND($F28="",NOT(ISNUMBER($E28))),"PU à saisir",ROUND(N($D28)*IF($F28&lt;&gt;"",$F28,$E28)*IF($G28="",1,IFERROR(INDEX(Majorations!$C$2:$C$3,MATCH($G28,ListeMajorations,0)),1)),2)))</f>
         <v/>
@@ -3243,7 +3185,7 @@
         <v/>
       </c>
       <c r="K28" s="0" t="str">
-        <f aca="false">IF(OR($J28="",$J28=0),"",IF(Grille="Proposition Circet",INDEX(BPU!$I$2:$I$117,$J28),INDEX(BPU!$H$2:$H$117,$J28)))</f>
+        <f aca="false">IF(OR($J28="",$J28=0),"",INDEX(BPU!$H$2:$H$117,$J28))</f>
         <v/>
       </c>
     </row>
@@ -3263,7 +3205,7 @@
         <v/>
       </c>
       <c r="F29" s="21"/>
-      <c r="G29" s="8"/>
+      <c r="G29" s="10"/>
       <c r="H29" s="22" t="str">
         <f aca="false">IF($B29="","",IF(AND($F29="",NOT(ISNUMBER($E29))),"PU à saisir",ROUND(N($D29)*IF($F29&lt;&gt;"",$F29,$E29)*IF($G29="",1,IFERROR(INDEX(Majorations!$C$2:$C$3,MATCH($G29,ListeMajorations,0)),1)),2)))</f>
         <v/>
@@ -3273,7 +3215,7 @@
         <v/>
       </c>
       <c r="K29" s="0" t="str">
-        <f aca="false">IF(OR($J29="",$J29=0),"",IF(Grille="Proposition Circet",INDEX(BPU!$I$2:$I$117,$J29),INDEX(BPU!$H$2:$H$117,$J29)))</f>
+        <f aca="false">IF(OR($J29="",$J29=0),"",INDEX(BPU!$H$2:$H$117,$J29))</f>
         <v/>
       </c>
     </row>
@@ -3293,7 +3235,7 @@
         <v/>
       </c>
       <c r="F30" s="21"/>
-      <c r="G30" s="8"/>
+      <c r="G30" s="10"/>
       <c r="H30" s="22" t="str">
         <f aca="false">IF($B30="","",IF(AND($F30="",NOT(ISNUMBER($E30))),"PU à saisir",ROUND(N($D30)*IF($F30&lt;&gt;"",$F30,$E30)*IF($G30="",1,IFERROR(INDEX(Majorations!$C$2:$C$3,MATCH($G30,ListeMajorations,0)),1)),2)))</f>
         <v/>
@@ -3303,7 +3245,7 @@
         <v/>
       </c>
       <c r="K30" s="0" t="str">
-        <f aca="false">IF(OR($J30="",$J30=0),"",IF(Grille="Proposition Circet",INDEX(BPU!$I$2:$I$117,$J30),INDEX(BPU!$H$2:$H$117,$J30)))</f>
+        <f aca="false">IF(OR($J30="",$J30=0),"",INDEX(BPU!$H$2:$H$117,$J30))</f>
         <v/>
       </c>
     </row>
@@ -3323,7 +3265,7 @@
         <v/>
       </c>
       <c r="F31" s="21"/>
-      <c r="G31" s="8"/>
+      <c r="G31" s="10"/>
       <c r="H31" s="22" t="str">
         <f aca="false">IF($B31="","",IF(AND($F31="",NOT(ISNUMBER($E31))),"PU à saisir",ROUND(N($D31)*IF($F31&lt;&gt;"",$F31,$E31)*IF($G31="",1,IFERROR(INDEX(Majorations!$C$2:$C$3,MATCH($G31,ListeMajorations,0)),1)),2)))</f>
         <v/>
@@ -3333,7 +3275,7 @@
         <v/>
       </c>
       <c r="K31" s="0" t="str">
-        <f aca="false">IF(OR($J31="",$J31=0),"",IF(Grille="Proposition Circet",INDEX(BPU!$I$2:$I$117,$J31),INDEX(BPU!$H$2:$H$117,$J31)))</f>
+        <f aca="false">IF(OR($J31="",$J31=0),"",INDEX(BPU!$H$2:$H$117,$J31))</f>
         <v/>
       </c>
     </row>
@@ -3353,7 +3295,7 @@
         <v/>
       </c>
       <c r="F32" s="21"/>
-      <c r="G32" s="8"/>
+      <c r="G32" s="10"/>
       <c r="H32" s="22" t="str">
         <f aca="false">IF($B32="","",IF(AND($F32="",NOT(ISNUMBER($E32))),"PU à saisir",ROUND(N($D32)*IF($F32&lt;&gt;"",$F32,$E32)*IF($G32="",1,IFERROR(INDEX(Majorations!$C$2:$C$3,MATCH($G32,ListeMajorations,0)),1)),2)))</f>
         <v/>
@@ -3363,7 +3305,7 @@
         <v/>
       </c>
       <c r="K32" s="0" t="str">
-        <f aca="false">IF(OR($J32="",$J32=0),"",IF(Grille="Proposition Circet",INDEX(BPU!$I$2:$I$117,$J32),INDEX(BPU!$H$2:$H$117,$J32)))</f>
+        <f aca="false">IF(OR($J32="",$J32=0),"",INDEX(BPU!$H$2:$H$117,$J32))</f>
         <v/>
       </c>
     </row>
@@ -3383,7 +3325,7 @@
         <v/>
       </c>
       <c r="F33" s="21"/>
-      <c r="G33" s="8"/>
+      <c r="G33" s="10"/>
       <c r="H33" s="22" t="str">
         <f aca="false">IF($B33="","",IF(AND($F33="",NOT(ISNUMBER($E33))),"PU à saisir",ROUND(N($D33)*IF($F33&lt;&gt;"",$F33,$E33)*IF($G33="",1,IFERROR(INDEX(Majorations!$C$2:$C$3,MATCH($G33,ListeMajorations,0)),1)),2)))</f>
         <v/>
@@ -3393,7 +3335,7 @@
         <v/>
       </c>
       <c r="K33" s="0" t="str">
-        <f aca="false">IF(OR($J33="",$J33=0),"",IF(Grille="Proposition Circet",INDEX(BPU!$I$2:$I$117,$J33),INDEX(BPU!$H$2:$H$117,$J33)))</f>
+        <f aca="false">IF(OR($J33="",$J33=0),"",INDEX(BPU!$H$2:$H$117,$J33))</f>
         <v/>
       </c>
     </row>
@@ -3413,7 +3355,7 @@
         <v/>
       </c>
       <c r="F34" s="21"/>
-      <c r="G34" s="8"/>
+      <c r="G34" s="10"/>
       <c r="H34" s="22" t="str">
         <f aca="false">IF($B34="","",IF(AND($F34="",NOT(ISNUMBER($E34))),"PU à saisir",ROUND(N($D34)*IF($F34&lt;&gt;"",$F34,$E34)*IF($G34="",1,IFERROR(INDEX(Majorations!$C$2:$C$3,MATCH($G34,ListeMajorations,0)),1)),2)))</f>
         <v/>
@@ -3423,7 +3365,7 @@
         <v/>
       </c>
       <c r="K34" s="0" t="str">
-        <f aca="false">IF(OR($J34="",$J34=0),"",IF(Grille="Proposition Circet",INDEX(BPU!$I$2:$I$117,$J34),INDEX(BPU!$H$2:$H$117,$J34)))</f>
+        <f aca="false">IF(OR($J34="",$J34=0),"",INDEX(BPU!$H$2:$H$117,$J34))</f>
         <v/>
       </c>
     </row>
@@ -3443,7 +3385,7 @@
         <v/>
       </c>
       <c r="F35" s="21"/>
-      <c r="G35" s="8"/>
+      <c r="G35" s="10"/>
       <c r="H35" s="22" t="str">
         <f aca="false">IF($B35="","",IF(AND($F35="",NOT(ISNUMBER($E35))),"PU à saisir",ROUND(N($D35)*IF($F35&lt;&gt;"",$F35,$E35)*IF($G35="",1,IFERROR(INDEX(Majorations!$C$2:$C$3,MATCH($G35,ListeMajorations,0)),1)),2)))</f>
         <v/>
@@ -3453,7 +3395,7 @@
         <v/>
       </c>
       <c r="K35" s="0" t="str">
-        <f aca="false">IF(OR($J35="",$J35=0),"",IF(Grille="Proposition Circet",INDEX(BPU!$I$2:$I$117,$J35),INDEX(BPU!$H$2:$H$117,$J35)))</f>
+        <f aca="false">IF(OR($J35="",$J35=0),"",INDEX(BPU!$H$2:$H$117,$J35))</f>
         <v/>
       </c>
     </row>
@@ -3473,7 +3415,7 @@
         <v/>
       </c>
       <c r="F36" s="21"/>
-      <c r="G36" s="8"/>
+      <c r="G36" s="10"/>
       <c r="H36" s="22" t="str">
         <f aca="false">IF($B36="","",IF(AND($F36="",NOT(ISNUMBER($E36))),"PU à saisir",ROUND(N($D36)*IF($F36&lt;&gt;"",$F36,$E36)*IF($G36="",1,IFERROR(INDEX(Majorations!$C$2:$C$3,MATCH($G36,ListeMajorations,0)),1)),2)))</f>
         <v/>
@@ -3483,7 +3425,7 @@
         <v/>
       </c>
       <c r="K36" s="0" t="str">
-        <f aca="false">IF(OR($J36="",$J36=0),"",IF(Grille="Proposition Circet",INDEX(BPU!$I$2:$I$117,$J36),INDEX(BPU!$H$2:$H$117,$J36)))</f>
+        <f aca="false">IF(OR($J36="",$J36=0),"",INDEX(BPU!$H$2:$H$117,$J36))</f>
         <v/>
       </c>
     </row>
@@ -3503,7 +3445,7 @@
         <v/>
       </c>
       <c r="F37" s="21"/>
-      <c r="G37" s="8"/>
+      <c r="G37" s="10"/>
       <c r="H37" s="22" t="str">
         <f aca="false">IF($B37="","",IF(AND($F37="",NOT(ISNUMBER($E37))),"PU à saisir",ROUND(N($D37)*IF($F37&lt;&gt;"",$F37,$E37)*IF($G37="",1,IFERROR(INDEX(Majorations!$C$2:$C$3,MATCH($G37,ListeMajorations,0)),1)),2)))</f>
         <v/>
@@ -3513,7 +3455,7 @@
         <v/>
       </c>
       <c r="K37" s="0" t="str">
-        <f aca="false">IF(OR($J37="",$J37=0),"",IF(Grille="Proposition Circet",INDEX(BPU!$I$2:$I$117,$J37),INDEX(BPU!$H$2:$H$117,$J37)))</f>
+        <f aca="false">IF(OR($J37="",$J37=0),"",INDEX(BPU!$H$2:$H$117,$J37))</f>
         <v/>
       </c>
     </row>
@@ -3533,7 +3475,7 @@
         <v/>
       </c>
       <c r="F38" s="21"/>
-      <c r="G38" s="8"/>
+      <c r="G38" s="10"/>
       <c r="H38" s="22" t="str">
         <f aca="false">IF($B38="","",IF(AND($F38="",NOT(ISNUMBER($E38))),"PU à saisir",ROUND(N($D38)*IF($F38&lt;&gt;"",$F38,$E38)*IF($G38="",1,IFERROR(INDEX(Majorations!$C$2:$C$3,MATCH($G38,ListeMajorations,0)),1)),2)))</f>
         <v/>
@@ -3543,7 +3485,7 @@
         <v/>
       </c>
       <c r="K38" s="0" t="str">
-        <f aca="false">IF(OR($J38="",$J38=0),"",IF(Grille="Proposition Circet",INDEX(BPU!$I$2:$I$117,$J38),INDEX(BPU!$H$2:$H$117,$J38)))</f>
+        <f aca="false">IF(OR($J38="",$J38=0),"",INDEX(BPU!$H$2:$H$117,$J38))</f>
         <v/>
       </c>
     </row>
@@ -3563,7 +3505,7 @@
         <v/>
       </c>
       <c r="F39" s="21"/>
-      <c r="G39" s="8"/>
+      <c r="G39" s="10"/>
       <c r="H39" s="22" t="str">
         <f aca="false">IF($B39="","",IF(AND($F39="",NOT(ISNUMBER($E39))),"PU à saisir",ROUND(N($D39)*IF($F39&lt;&gt;"",$F39,$E39)*IF($G39="",1,IFERROR(INDEX(Majorations!$C$2:$C$3,MATCH($G39,ListeMajorations,0)),1)),2)))</f>
         <v/>
@@ -3573,7 +3515,7 @@
         <v/>
       </c>
       <c r="K39" s="0" t="str">
-        <f aca="false">IF(OR($J39="",$J39=0),"",IF(Grille="Proposition Circet",INDEX(BPU!$I$2:$I$117,$J39),INDEX(BPU!$H$2:$H$117,$J39)))</f>
+        <f aca="false">IF(OR($J39="",$J39=0),"",INDEX(BPU!$H$2:$H$117,$J39))</f>
         <v/>
       </c>
     </row>
@@ -3593,7 +3535,7 @@
         <v/>
       </c>
       <c r="F40" s="21"/>
-      <c r="G40" s="8"/>
+      <c r="G40" s="10"/>
       <c r="H40" s="22" t="str">
         <f aca="false">IF($B40="","",IF(AND($F40="",NOT(ISNUMBER($E40))),"PU à saisir",ROUND(N($D40)*IF($F40&lt;&gt;"",$F40,$E40)*IF($G40="",1,IFERROR(INDEX(Majorations!$C$2:$C$3,MATCH($G40,ListeMajorations,0)),1)),2)))</f>
         <v/>
@@ -3603,7 +3545,7 @@
         <v/>
       </c>
       <c r="K40" s="0" t="str">
-        <f aca="false">IF(OR($J40="",$J40=0),"",IF(Grille="Proposition Circet",INDEX(BPU!$I$2:$I$117,$J40),INDEX(BPU!$H$2:$H$117,$J40)))</f>
+        <f aca="false">IF(OR($J40="",$J40=0),"",INDEX(BPU!$H$2:$H$117,$J40))</f>
         <v/>
       </c>
     </row>
@@ -3623,7 +3565,7 @@
         <v/>
       </c>
       <c r="F41" s="21"/>
-      <c r="G41" s="8"/>
+      <c r="G41" s="10"/>
       <c r="H41" s="22" t="str">
         <f aca="false">IF($B41="","",IF(AND($F41="",NOT(ISNUMBER($E41))),"PU à saisir",ROUND(N($D41)*IF($F41&lt;&gt;"",$F41,$E41)*IF($G41="",1,IFERROR(INDEX(Majorations!$C$2:$C$3,MATCH($G41,ListeMajorations,0)),1)),2)))</f>
         <v/>
@@ -3633,7 +3575,7 @@
         <v/>
       </c>
       <c r="K41" s="0" t="str">
-        <f aca="false">IF(OR($J41="",$J41=0),"",IF(Grille="Proposition Circet",INDEX(BPU!$I$2:$I$117,$J41),INDEX(BPU!$H$2:$H$117,$J41)))</f>
+        <f aca="false">IF(OR($J41="",$J41=0),"",INDEX(BPU!$H$2:$H$117,$J41))</f>
         <v/>
       </c>
     </row>
@@ -3653,7 +3595,7 @@
         <v/>
       </c>
       <c r="F42" s="21"/>
-      <c r="G42" s="8"/>
+      <c r="G42" s="10"/>
       <c r="H42" s="22" t="str">
         <f aca="false">IF($B42="","",IF(AND($F42="",NOT(ISNUMBER($E42))),"PU à saisir",ROUND(N($D42)*IF($F42&lt;&gt;"",$F42,$E42)*IF($G42="",1,IFERROR(INDEX(Majorations!$C$2:$C$3,MATCH($G42,ListeMajorations,0)),1)),2)))</f>
         <v/>
@@ -3663,7 +3605,7 @@
         <v/>
       </c>
       <c r="K42" s="0" t="str">
-        <f aca="false">IF(OR($J42="",$J42=0),"",IF(Grille="Proposition Circet",INDEX(BPU!$I$2:$I$117,$J42),INDEX(BPU!$H$2:$H$117,$J42)))</f>
+        <f aca="false">IF(OR($J42="",$J42=0),"",INDEX(BPU!$H$2:$H$117,$J42))</f>
         <v/>
       </c>
     </row>
@@ -3683,7 +3625,7 @@
         <v/>
       </c>
       <c r="F43" s="21"/>
-      <c r="G43" s="8"/>
+      <c r="G43" s="10"/>
       <c r="H43" s="22" t="str">
         <f aca="false">IF($B43="","",IF(AND($F43="",NOT(ISNUMBER($E43))),"PU à saisir",ROUND(N($D43)*IF($F43&lt;&gt;"",$F43,$E43)*IF($G43="",1,IFERROR(INDEX(Majorations!$C$2:$C$3,MATCH($G43,ListeMajorations,0)),1)),2)))</f>
         <v/>
@@ -3693,7 +3635,7 @@
         <v/>
       </c>
       <c r="K43" s="0" t="str">
-        <f aca="false">IF(OR($J43="",$J43=0),"",IF(Grille="Proposition Circet",INDEX(BPU!$I$2:$I$117,$J43),INDEX(BPU!$H$2:$H$117,$J43)))</f>
+        <f aca="false">IF(OR($J43="",$J43=0),"",INDEX(BPU!$H$2:$H$117,$J43))</f>
         <v/>
       </c>
     </row>
@@ -3713,7 +3655,7 @@
         <v/>
       </c>
       <c r="F44" s="21"/>
-      <c r="G44" s="8"/>
+      <c r="G44" s="10"/>
       <c r="H44" s="22" t="str">
         <f aca="false">IF($B44="","",IF(AND($F44="",NOT(ISNUMBER($E44))),"PU à saisir",ROUND(N($D44)*IF($F44&lt;&gt;"",$F44,$E44)*IF($G44="",1,IFERROR(INDEX(Majorations!$C$2:$C$3,MATCH($G44,ListeMajorations,0)),1)),2)))</f>
         <v/>
@@ -3723,7 +3665,7 @@
         <v/>
       </c>
       <c r="K44" s="0" t="str">
-        <f aca="false">IF(OR($J44="",$J44=0),"",IF(Grille="Proposition Circet",INDEX(BPU!$I$2:$I$117,$J44),INDEX(BPU!$H$2:$H$117,$J44)))</f>
+        <f aca="false">IF(OR($J44="",$J44=0),"",INDEX(BPU!$H$2:$H$117,$J44))</f>
         <v/>
       </c>
     </row>
@@ -3738,7 +3680,7 @@
       <c r="E46" s="24"/>
       <c r="F46" s="24"/>
       <c r="G46" s="25" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H46" s="26" t="n">
         <f aca="false">SUM(H15:H44)</f>
@@ -3775,7 +3717,7 @@
       <c r="E48" s="27"/>
       <c r="F48" s="27"/>
       <c r="G48" s="28" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="H48" s="29" t="n">
         <f aca="false">H46+H47</f>
@@ -3784,7 +3726,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="13" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B50" s="13"/>
       <c r="C50" s="13"/>
@@ -3796,7 +3738,7 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B51" s="4"/>
       <c r="C51" s="4"/>
@@ -3808,7 +3750,7 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="4" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B52" s="4"/>
       <c r="C52" s="4"/>
@@ -3820,7 +3762,7 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="4" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B53" s="4"/>
       <c r="C53" s="4"/>
@@ -3845,11 +3787,11 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="31" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B56" s="31"/>
       <c r="E56" s="31" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F56" s="31"/>
       <c r="G56" s="31"/>
@@ -3944,7 +3886,7 @@
       <formula>$H15="PU à saisir"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="5">
+  <dataValidations count="4">
     <dataValidation allowBlank="true" error="Cette prestation n'est pas dans le BPU. Continuer pour la saisir quand même (indiquer alors un PU HT sur devis)." errorStyle="warning" errorTitle="Prestation hors BPU" operator="between" prompt="Choisir dans la liste (ou taper le code pour la retrouver)." promptTitle="Prestation" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B15:B44" type="list">
       <formula1>ListePrestations</formula1>
       <formula2>0</formula2>
@@ -3957,11 +3899,7 @@
       <formula1>0</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="N2" type="list">
-      <formula1>"Prix BPU Axione,Proposition Circet"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="N4" type="list">
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="N3" type="list">
       <formula1>"Non,Oui"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -3982,7 +3920,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:L117"/>
+  <dimension ref="A1:K117"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -3991,4220 +3929,3881 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="60"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="50"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="70"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="70"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="42"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="B1" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="C1" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="D1" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="E1" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="F1" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="E1" s="16" t="s">
+      <c r="G1" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="H1" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="F1" s="16" t="s">
+      <c r="I1" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="G1" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="H1" s="16" t="s">
+      <c r="J1" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="I1" s="16" t="s">
+      <c r="K1" s="16" t="s">
         <v>71</v>
-      </c>
-      <c r="J1" s="16" t="s">
-        <v>72</v>
-      </c>
-      <c r="K1" s="16" t="s">
-        <v>73</v>
-      </c>
-      <c r="L1" s="16" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="33" t="s">
+        <v>72</v>
+      </c>
+      <c r="B2" s="33" t="s">
+        <v>73</v>
+      </c>
+      <c r="C2" s="33" t="s">
+        <v>74</v>
+      </c>
+      <c r="D2" s="33" t="s">
         <v>75</v>
       </c>
-      <c r="B2" s="33" t="s">
+      <c r="E2" s="34" t="s">
         <v>76</v>
       </c>
-      <c r="C2" s="33" t="s">
+      <c r="F2" s="33" t="s">
         <v>77</v>
       </c>
-      <c r="D2" s="33" t="s">
+      <c r="G2" s="33" t="s">
         <v>78</v>
-      </c>
-      <c r="E2" s="34" t="s">
-        <v>79</v>
-      </c>
-      <c r="F2" s="33" t="s">
-        <v>80</v>
-      </c>
-      <c r="G2" s="33" t="s">
-        <v>81</v>
       </c>
       <c r="H2" s="35" t="n">
         <v>210</v>
       </c>
-      <c r="I2" s="35" t="n">
-        <v>210</v>
+      <c r="I2" s="33" t="s">
+        <v>79</v>
       </c>
       <c r="J2" s="33" t="s">
-        <v>82</v>
+        <v>47</v>
       </c>
       <c r="K2" s="33" t="s">
-        <v>48</v>
-      </c>
-      <c r="L2" s="33" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="33" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B3" s="33" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C3" s="33" t="s">
+        <v>74</v>
+      </c>
+      <c r="D3" s="33" t="s">
+        <v>81</v>
+      </c>
+      <c r="E3" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="F3" s="33" t="s">
         <v>77</v>
       </c>
-      <c r="D3" s="33" t="s">
-        <v>84</v>
-      </c>
-      <c r="E3" s="34" t="s">
-        <v>85</v>
-      </c>
-      <c r="F3" s="33" t="s">
-        <v>80</v>
-      </c>
       <c r="G3" s="33" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="H3" s="35" t="n">
         <v>210</v>
       </c>
-      <c r="I3" s="35" t="n">
-        <v>210</v>
+      <c r="I3" s="33" t="s">
+        <v>79</v>
       </c>
       <c r="J3" s="33" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K3" s="33" t="s">
-        <v>86</v>
-      </c>
-      <c r="L3" s="33" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="33" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B4" s="33" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C4" s="33" t="s">
+        <v>74</v>
+      </c>
+      <c r="D4" s="33" t="s">
+        <v>85</v>
+      </c>
+      <c r="E4" s="34" t="s">
+        <v>86</v>
+      </c>
+      <c r="F4" s="33" t="s">
         <v>77</v>
       </c>
-      <c r="D4" s="33" t="s">
-        <v>88</v>
-      </c>
-      <c r="E4" s="34" t="s">
-        <v>89</v>
-      </c>
-      <c r="F4" s="33" t="s">
-        <v>80</v>
-      </c>
       <c r="G4" s="33" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="H4" s="35" t="n">
         <v>210</v>
       </c>
-      <c r="I4" s="35" t="n">
-        <v>210</v>
+      <c r="I4" s="33" t="s">
+        <v>79</v>
       </c>
       <c r="J4" s="33" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="K4" s="33" t="s">
-        <v>90</v>
-      </c>
-      <c r="L4" s="33" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="33" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B5" s="33" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C5" s="33" t="s">
+        <v>74</v>
+      </c>
+      <c r="D5" s="33" t="s">
+        <v>89</v>
+      </c>
+      <c r="E5" s="34" t="s">
+        <v>90</v>
+      </c>
+      <c r="F5" s="33" t="s">
         <v>77</v>
       </c>
-      <c r="D5" s="33" t="s">
-        <v>92</v>
-      </c>
-      <c r="E5" s="34" t="s">
-        <v>93</v>
-      </c>
-      <c r="F5" s="33" t="s">
-        <v>80</v>
-      </c>
       <c r="G5" s="33" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="H5" s="35" t="n">
         <v>210</v>
       </c>
-      <c r="I5" s="35" t="n">
-        <v>210</v>
+      <c r="I5" s="33" t="s">
+        <v>79</v>
       </c>
       <c r="J5" s="33" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K5" s="33" t="s">
-        <v>94</v>
-      </c>
-      <c r="L5" s="33" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="33" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B6" s="33" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C6" s="33" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D6" s="33" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E6" s="34" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="F6" s="33" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="G6" s="33" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="H6" s="35" t="n">
         <v>459.51</v>
       </c>
-      <c r="I6" s="35" t="n">
-        <v>459.51</v>
+      <c r="I6" s="33" t="s">
+        <v>79</v>
       </c>
       <c r="J6" s="33" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="K6" s="33" t="s">
-        <v>100</v>
-      </c>
-      <c r="L6" s="33" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="33" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B7" s="33" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C7" s="33" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D7" s="33" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E7" s="34" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="F7" s="33" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="G7" s="33" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="H7" s="35" t="n">
         <v>0.93</v>
       </c>
-      <c r="I7" s="35" t="n">
-        <v>0.93</v>
+      <c r="I7" s="33" t="s">
+        <v>101</v>
       </c>
       <c r="J7" s="33" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="K7" s="33" t="s">
-        <v>106</v>
-      </c>
-      <c r="L7" s="33" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="33" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B8" s="33" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C8" s="33" t="s">
+        <v>74</v>
+      </c>
+      <c r="D8" s="33" t="s">
+        <v>103</v>
+      </c>
+      <c r="E8" s="34" t="s">
+        <v>104</v>
+      </c>
+      <c r="F8" s="33" t="s">
         <v>77</v>
       </c>
-      <c r="D8" s="33" t="s">
-        <v>107</v>
-      </c>
-      <c r="E8" s="34" t="s">
-        <v>108</v>
-      </c>
-      <c r="F8" s="33" t="s">
-        <v>109</v>
-      </c>
       <c r="G8" s="33" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="H8" s="35" t="n">
         <v>210</v>
       </c>
-      <c r="I8" s="35" t="n">
-        <v>210</v>
+      <c r="I8" s="33" t="s">
+        <v>79</v>
       </c>
       <c r="J8" s="33" t="s">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="K8" s="33" t="s">
-        <v>110</v>
-      </c>
-      <c r="L8" s="33" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="33" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B9" s="33" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C9" s="33" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D9" s="33" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E9" s="34" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="F9" s="33" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="G9" s="33" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="H9" s="35" t="n">
         <v>50.1875</v>
       </c>
-      <c r="I9" s="35" t="n">
-        <v>65</v>
+      <c r="I9" s="33" t="s">
+        <v>79</v>
       </c>
       <c r="J9" s="33" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="K9" s="33" t="s">
-        <v>115</v>
-      </c>
-      <c r="L9" s="33" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="33" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B10" s="33" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C10" s="33" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D10" s="33" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="E10" s="34" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="F10" s="33" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="G10" s="33" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="H10" s="35" t="n">
         <v>50.1875</v>
       </c>
-      <c r="I10" s="35" t="n">
-        <v>65</v>
+      <c r="I10" s="33" t="s">
+        <v>79</v>
       </c>
       <c r="J10" s="33" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="K10" s="33" t="s">
-        <v>118</v>
-      </c>
-      <c r="L10" s="33" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="33" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B11" s="33" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C11" s="33" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D11" s="33" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="E11" s="34" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="F11" s="33" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="G11" s="33" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="H11" s="35" t="n">
         <v>50.1875</v>
       </c>
-      <c r="I11" s="35" t="n">
-        <v>65</v>
+      <c r="I11" s="33" t="s">
+        <v>79</v>
       </c>
       <c r="J11" s="33" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="K11" s="33" t="s">
-        <v>122</v>
-      </c>
-      <c r="L11" s="33" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="33" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B12" s="33" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C12" s="33" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D12" s="33" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="E12" s="34" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="F12" s="33"/>
       <c r="G12" s="33" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="H12" s="35" t="s">
-        <v>126</v>
-      </c>
-      <c r="I12" s="35" t="s">
-        <v>126</v>
+        <v>120</v>
+      </c>
+      <c r="I12" s="33" t="s">
+        <v>79</v>
       </c>
       <c r="J12" s="33" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="K12" s="33" t="s">
-        <v>127</v>
-      </c>
-      <c r="L12" s="33" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="33" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B13" s="33" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C13" s="33" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D13" s="33" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="E13" s="34" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="F13" s="33"/>
       <c r="G13" s="33" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="H13" s="35" t="s">
-        <v>126</v>
-      </c>
-      <c r="I13" s="35" t="s">
-        <v>126</v>
+        <v>120</v>
+      </c>
+      <c r="I13" s="33" t="s">
+        <v>79</v>
       </c>
       <c r="J13" s="33" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="K13" s="33" t="s">
-        <v>130</v>
-      </c>
-      <c r="L13" s="33" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="33" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B14" s="33" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C14" s="33" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D14" s="33" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="E14" s="34" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="F14" s="33"/>
       <c r="G14" s="33" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="H14" s="35" t="s">
-        <v>126</v>
-      </c>
-      <c r="I14" s="35" t="s">
-        <v>126</v>
+        <v>120</v>
+      </c>
+      <c r="I14" s="33" t="s">
+        <v>79</v>
       </c>
       <c r="J14" s="33" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="K14" s="33" t="s">
-        <v>133</v>
-      </c>
-      <c r="L14" s="33" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="33" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B15" s="33" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="C15" s="33" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="D15" s="33" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="E15" s="34" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="F15" s="33"/>
       <c r="G15" s="33" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="H15" s="35" t="n">
         <v>500</v>
       </c>
-      <c r="I15" s="35" t="n">
-        <v>500</v>
+      <c r="I15" s="33" t="s">
+        <v>134</v>
       </c>
       <c r="J15" s="33" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="K15" s="33" t="s">
-        <v>141</v>
-      </c>
-      <c r="L15" s="33" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="33" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B16" s="33" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="C16" s="33" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="D16" s="33" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="E16" s="34" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="F16" s="33"/>
       <c r="G16" s="33" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="H16" s="35" t="n">
         <v>300</v>
       </c>
-      <c r="I16" s="35" t="n">
-        <v>500</v>
+      <c r="I16" s="33" t="s">
+        <v>134</v>
       </c>
       <c r="J16" s="33" t="s">
+        <v>139</v>
+      </c>
+      <c r="K16" s="33" t="s">
         <v>140</v>
-      </c>
-      <c r="K16" s="33" t="s">
-        <v>145</v>
-      </c>
-      <c r="L16" s="33" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="33" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B17" s="33" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="C17" s="33" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="D17" s="33" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="E17" s="34" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="F17" s="33"/>
       <c r="G17" s="33" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="H17" s="35" t="n">
         <v>160.341790896159</v>
       </c>
-      <c r="I17" s="35" t="n">
-        <v>160.341790896159</v>
+      <c r="I17" s="33" t="s">
+        <v>79</v>
       </c>
       <c r="J17" s="33" t="s">
-        <v>114</v>
+        <v>48</v>
       </c>
       <c r="K17" s="33" t="s">
-        <v>50</v>
-      </c>
-      <c r="L17" s="33" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="33" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B18" s="33" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="C18" s="33" t="s">
+        <v>141</v>
+      </c>
+      <c r="D18" s="33" t="s">
+        <v>146</v>
+      </c>
+      <c r="E18" s="34" t="s">
         <v>147</v>
-      </c>
-      <c r="D18" s="33" t="s">
-        <v>152</v>
-      </c>
-      <c r="E18" s="34" t="s">
-        <v>153</v>
       </c>
       <c r="F18" s="33"/>
       <c r="G18" s="33" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="H18" s="35" t="n">
         <v>137.720957325747</v>
       </c>
-      <c r="I18" s="35" t="n">
-        <v>137.720957325747</v>
+      <c r="I18" s="33" t="s">
+        <v>79</v>
       </c>
       <c r="J18" s="33" t="s">
-        <v>114</v>
+        <v>148</v>
       </c>
       <c r="K18" s="33" t="s">
-        <v>154</v>
-      </c>
-      <c r="L18" s="33" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="33" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B19" s="33" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="C19" s="33" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="D19" s="33" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="E19" s="34" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="F19" s="33"/>
       <c r="G19" s="33" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="H19" s="35" t="n">
         <v>141.71286913229</v>
       </c>
-      <c r="I19" s="35" t="n">
-        <v>141.71286913229</v>
+      <c r="I19" s="33" t="s">
+        <v>79</v>
       </c>
       <c r="J19" s="33" t="s">
-        <v>114</v>
+        <v>152</v>
       </c>
       <c r="K19" s="33" t="s">
-        <v>158</v>
-      </c>
-      <c r="L19" s="33" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="33" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B20" s="33" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="C20" s="33" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="D20" s="33" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="E20" s="34" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="F20" s="33"/>
       <c r="G20" s="33" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="H20" s="35" t="n">
         <v>86.4914224751066</v>
       </c>
-      <c r="I20" s="35" t="n">
-        <v>86.4914224751066</v>
+      <c r="I20" s="33" t="s">
+        <v>79</v>
       </c>
       <c r="J20" s="33" t="s">
-        <v>114</v>
+        <v>156</v>
       </c>
       <c r="K20" s="33" t="s">
-        <v>162</v>
-      </c>
-      <c r="L20" s="33" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="33" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B21" s="33" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="C21" s="33" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="D21" s="33" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="E21" s="34" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="F21" s="33"/>
       <c r="G21" s="33" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="H21" s="35" t="n">
         <v>50.5</v>
       </c>
-      <c r="I21" s="35" t="n">
-        <v>60</v>
+      <c r="I21" s="33" t="s">
+        <v>79</v>
       </c>
       <c r="J21" s="33" t="s">
-        <v>114</v>
+        <v>160</v>
       </c>
       <c r="K21" s="33" t="s">
-        <v>166</v>
-      </c>
-      <c r="L21" s="33" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="33" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B22" s="33" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="C22" s="33" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="D22" s="33" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="E22" s="34" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="F22" s="33"/>
       <c r="G22" s="33" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="H22" s="35" t="n">
         <v>163.62</v>
       </c>
-      <c r="I22" s="35" t="n">
-        <v>163.62</v>
+      <c r="I22" s="33" t="s">
+        <v>79</v>
       </c>
       <c r="J22" s="33" t="s">
-        <v>114</v>
+        <v>164</v>
       </c>
       <c r="K22" s="33" t="s">
-        <v>170</v>
-      </c>
-      <c r="L22" s="33" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="33" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B23" s="33" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="C23" s="33" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="D23" s="33" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="E23" s="34" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="F23" s="33"/>
       <c r="G23" s="33" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="H23" s="35" t="n">
         <v>50.5</v>
       </c>
-      <c r="I23" s="35" t="n">
-        <v>60</v>
+      <c r="I23" s="33" t="s">
+        <v>79</v>
       </c>
       <c r="J23" s="33" t="s">
-        <v>114</v>
+        <v>168</v>
       </c>
       <c r="K23" s="33" t="s">
-        <v>174</v>
-      </c>
-      <c r="L23" s="33" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="33" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B24" s="33" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="C24" s="33" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="D24" s="33" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="E24" s="34" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="F24" s="33"/>
       <c r="G24" s="33" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="H24" s="35" t="n">
         <v>163.62</v>
       </c>
-      <c r="I24" s="35" t="n">
-        <v>163.62</v>
+      <c r="I24" s="33" t="s">
+        <v>79</v>
       </c>
       <c r="J24" s="33" t="s">
-        <v>114</v>
+        <v>172</v>
       </c>
       <c r="K24" s="33" t="s">
-        <v>178</v>
-      </c>
-      <c r="L24" s="33" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="33" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B25" s="33" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="C25" s="33" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="D25" s="33" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="E25" s="34" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="F25" s="33"/>
       <c r="G25" s="33" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="H25" s="35" t="n">
         <v>35.92625</v>
       </c>
-      <c r="I25" s="35" t="n">
-        <v>38</v>
+      <c r="I25" s="33" t="s">
+        <v>79</v>
       </c>
       <c r="J25" s="33" t="s">
-        <v>114</v>
+        <v>50</v>
       </c>
       <c r="K25" s="33" t="s">
-        <v>52</v>
-      </c>
-      <c r="L25" s="33" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="33" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B26" s="33" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="C26" s="33" t="s">
+        <v>174</v>
+      </c>
+      <c r="D26" s="33" t="s">
+        <v>179</v>
+      </c>
+      <c r="E26" s="34" t="s">
         <v>180</v>
-      </c>
-      <c r="D26" s="33" t="s">
-        <v>185</v>
-      </c>
-      <c r="E26" s="34" t="s">
-        <v>186</v>
       </c>
       <c r="F26" s="33"/>
       <c r="G26" s="33" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="H26" s="35" t="n">
         <v>35.05125</v>
       </c>
-      <c r="I26" s="35" t="n">
-        <v>38</v>
+      <c r="I26" s="33" t="s">
+        <v>79</v>
       </c>
       <c r="J26" s="33" t="s">
-        <v>114</v>
+        <v>181</v>
       </c>
       <c r="K26" s="33" t="s">
-        <v>187</v>
-      </c>
-      <c r="L26" s="33" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="33" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B27" s="33" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="C27" s="33" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="D27" s="33" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="E27" s="34" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="F27" s="33"/>
       <c r="G27" s="33" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="H27" s="35" t="n">
         <v>55.17</v>
       </c>
-      <c r="I27" s="35" t="n">
-        <v>57</v>
+      <c r="I27" s="33" t="s">
+        <v>79</v>
       </c>
       <c r="J27" s="33" t="s">
-        <v>114</v>
+        <v>185</v>
       </c>
       <c r="K27" s="33" t="s">
-        <v>191</v>
-      </c>
-      <c r="L27" s="33" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="33" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B28" s="33" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="C28" s="33" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="D28" s="33" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="E28" s="34" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="F28" s="33"/>
       <c r="G28" s="33" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="H28" s="35" t="n">
         <v>73.72</v>
       </c>
-      <c r="I28" s="35" t="n">
-        <v>86</v>
+      <c r="I28" s="33" t="s">
+        <v>79</v>
       </c>
       <c r="J28" s="33" t="s">
-        <v>114</v>
+        <v>189</v>
       </c>
       <c r="K28" s="33" t="s">
-        <v>195</v>
-      </c>
-      <c r="L28" s="33" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="33" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B29" s="33" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="C29" s="33" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="D29" s="33" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="E29" s="34" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="F29" s="33"/>
       <c r="G29" s="33" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="H29" s="35" t="n">
         <v>123.75</v>
       </c>
-      <c r="I29" s="35" t="n">
-        <v>123.75</v>
+      <c r="I29" s="33" t="s">
+        <v>79</v>
       </c>
       <c r="J29" s="33" t="s">
-        <v>114</v>
+        <v>193</v>
       </c>
       <c r="K29" s="33" t="s">
-        <v>199</v>
-      </c>
-      <c r="L29" s="33" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="33" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B30" s="33" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="C30" s="33" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="D30" s="33" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="E30" s="34" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="F30" s="33"/>
       <c r="G30" s="33" t="s">
-        <v>203</v>
-      </c>
-      <c r="H30" s="35" t="n">
-        <v>23.2861522048364</v>
-      </c>
-      <c r="I30" s="35" t="s">
-        <v>126</v>
+        <v>197</v>
+      </c>
+      <c r="H30" s="35" t="s">
+        <v>120</v>
+      </c>
+      <c r="I30" s="33" t="s">
+        <v>79</v>
       </c>
       <c r="J30" s="33" t="s">
-        <v>114</v>
+        <v>198</v>
       </c>
       <c r="K30" s="33" t="s">
-        <v>204</v>
-      </c>
-      <c r="L30" s="33" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="33" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B31" s="33" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="C31" s="33" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="D31" s="33" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="E31" s="34" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="F31" s="33"/>
       <c r="G31" s="33" t="s">
-        <v>209</v>
-      </c>
-      <c r="H31" s="35" t="n">
-        <v>883.543146514936</v>
-      </c>
-      <c r="I31" s="35" t="s">
-        <v>126</v>
+        <v>203</v>
+      </c>
+      <c r="H31" s="35" t="s">
+        <v>120</v>
+      </c>
+      <c r="I31" s="33" t="s">
+        <v>79</v>
       </c>
       <c r="J31" s="33" t="s">
-        <v>114</v>
+        <v>204</v>
       </c>
       <c r="K31" s="33" t="s">
-        <v>210</v>
-      </c>
-      <c r="L31" s="33" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="33" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B32" s="33" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="C32" s="33" t="s">
+        <v>200</v>
+      </c>
+      <c r="D32" s="33" t="s">
         <v>206</v>
       </c>
-      <c r="D32" s="33" t="s">
-        <v>212</v>
-      </c>
       <c r="E32" s="34" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="F32" s="33"/>
       <c r="G32" s="33" t="s">
+        <v>203</v>
+      </c>
+      <c r="H32" s="35" t="s">
+        <v>120</v>
+      </c>
+      <c r="I32" s="33" t="s">
+        <v>79</v>
+      </c>
+      <c r="J32" s="33" t="s">
+        <v>208</v>
+      </c>
+      <c r="K32" s="33" t="s">
         <v>209</v>
-      </c>
-      <c r="H32" s="35" t="n">
-        <v>276.164756756757</v>
-      </c>
-      <c r="I32" s="35" t="s">
-        <v>126</v>
-      </c>
-      <c r="J32" s="33" t="s">
-        <v>114</v>
-      </c>
-      <c r="K32" s="33" t="s">
-        <v>214</v>
-      </c>
-      <c r="L32" s="33" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="33" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B33" s="33" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="C33" s="33" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="D33" s="33" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="E33" s="34" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="F33" s="33"/>
       <c r="G33" s="33" t="s">
-        <v>209</v>
-      </c>
-      <c r="H33" s="35" t="n">
-        <v>190.976837837838</v>
-      </c>
-      <c r="I33" s="35" t="s">
-        <v>126</v>
+        <v>203</v>
+      </c>
+      <c r="H33" s="35" t="s">
+        <v>120</v>
+      </c>
+      <c r="I33" s="33" t="s">
+        <v>79</v>
       </c>
       <c r="J33" s="33" t="s">
-        <v>114</v>
+        <v>212</v>
       </c>
       <c r="K33" s="33" t="s">
-        <v>218</v>
-      </c>
-      <c r="L33" s="33" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="33" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B34" s="33" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="C34" s="33" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="D34" s="33" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="E34" s="34" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="F34" s="33"/>
       <c r="G34" s="33" t="s">
-        <v>209</v>
-      </c>
-      <c r="H34" s="35" t="n">
-        <v>217.559193456614</v>
-      </c>
-      <c r="I34" s="35" t="s">
-        <v>126</v>
+        <v>203</v>
+      </c>
+      <c r="H34" s="35" t="s">
+        <v>120</v>
+      </c>
+      <c r="I34" s="33" t="s">
+        <v>79</v>
       </c>
       <c r="J34" s="33" t="s">
-        <v>114</v>
+        <v>216</v>
       </c>
       <c r="K34" s="33" t="s">
-        <v>222</v>
-      </c>
-      <c r="L34" s="33" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="33" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B35" s="33" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="C35" s="33" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="D35" s="33" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E35" s="34" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="F35" s="33"/>
       <c r="G35" s="33" t="s">
-        <v>209</v>
-      </c>
-      <c r="H35" s="35" t="n">
-        <v>1246.14180227596</v>
-      </c>
-      <c r="I35" s="35" t="s">
-        <v>126</v>
+        <v>203</v>
+      </c>
+      <c r="H35" s="35" t="s">
+        <v>120</v>
+      </c>
+      <c r="I35" s="33" t="s">
+        <v>79</v>
       </c>
       <c r="J35" s="33" t="s">
-        <v>114</v>
+        <v>220</v>
       </c>
       <c r="K35" s="33" t="s">
-        <v>226</v>
-      </c>
-      <c r="L35" s="33" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="33" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B36" s="33" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="C36" s="33" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="D36" s="33" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="E36" s="34" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="F36" s="33"/>
       <c r="G36" s="33" t="s">
-        <v>209</v>
-      </c>
-      <c r="H36" s="35" t="n">
-        <v>1013.2802802276</v>
-      </c>
-      <c r="I36" s="35" t="s">
-        <v>126</v>
+        <v>203</v>
+      </c>
+      <c r="H36" s="35" t="s">
+        <v>120</v>
+      </c>
+      <c r="I36" s="33" t="s">
+        <v>79</v>
       </c>
       <c r="J36" s="33" t="s">
-        <v>114</v>
+        <v>224</v>
       </c>
       <c r="K36" s="33" t="s">
-        <v>230</v>
-      </c>
-      <c r="L36" s="33" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="36" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="B37" s="36" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="C37" s="36" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="D37" s="36" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="E37" s="34" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="F37" s="33" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="G37" s="33" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="H37" s="35" t="n">
         <v>0.4</v>
       </c>
-      <c r="I37" s="35" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="J37" s="33"/>
+      <c r="I37" s="33"/>
+      <c r="J37" s="33" t="s">
+        <v>231</v>
+      </c>
       <c r="K37" s="33" t="s">
-        <v>237</v>
-      </c>
-      <c r="L37" s="33" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="36" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="B38" s="36" t="s">
+        <v>227</v>
+      </c>
+      <c r="C38" s="36" t="s">
+        <v>227</v>
+      </c>
+      <c r="D38" s="36" t="s">
         <v>233</v>
       </c>
-      <c r="C38" s="36" t="s">
-        <v>233</v>
-      </c>
-      <c r="D38" s="36" t="s">
-        <v>239</v>
-      </c>
       <c r="E38" s="34" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="F38" s="33" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="G38" s="33" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="H38" s="35" t="n">
         <v>550</v>
       </c>
-      <c r="I38" s="35" t="s">
-        <v>126</v>
-      </c>
-      <c r="J38" s="33"/>
+      <c r="I38" s="33"/>
+      <c r="J38" s="33" t="s">
+        <v>237</v>
+      </c>
       <c r="K38" s="33" t="s">
-        <v>243</v>
-      </c>
-      <c r="L38" s="33" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="36" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="B39" s="36" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="C39" s="36" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="D39" s="36" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="E39" s="34" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="F39" s="33"/>
       <c r="G39" s="33" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="H39" s="35" t="n">
         <v>25</v>
       </c>
-      <c r="I39" s="35" t="n">
-        <v>38.48</v>
-      </c>
-      <c r="J39" s="33"/>
+      <c r="I39" s="33"/>
+      <c r="J39" s="33" t="s">
+        <v>241</v>
+      </c>
       <c r="K39" s="33" t="s">
-        <v>247</v>
-      </c>
-      <c r="L39" s="33" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="36" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="B40" s="36" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="C40" s="36" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="D40" s="36" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="E40" s="34" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="F40" s="33"/>
       <c r="G40" s="33" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="H40" s="35" t="n">
         <v>35</v>
       </c>
-      <c r="I40" s="35" t="n">
-        <v>45</v>
-      </c>
-      <c r="J40" s="33"/>
+      <c r="I40" s="33"/>
+      <c r="J40" s="33" t="s">
+        <v>245</v>
+      </c>
       <c r="K40" s="33" t="s">
-        <v>251</v>
-      </c>
-      <c r="L40" s="33" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="36" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="B41" s="36" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="C41" s="36" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="D41" s="36" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="E41" s="34" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="F41" s="33" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="G41" s="33" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="H41" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="I41" s="35" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="J41" s="33"/>
+      <c r="I41" s="33"/>
+      <c r="J41" s="33" t="s">
+        <v>51</v>
+      </c>
       <c r="K41" s="33" t="s">
-        <v>53</v>
-      </c>
-      <c r="L41" s="33" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="36" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="B42" s="36" t="s">
+        <v>247</v>
+      </c>
+      <c r="C42" s="36" t="s">
+        <v>248</v>
+      </c>
+      <c r="D42" s="36" t="s">
         <v>253</v>
       </c>
-      <c r="C42" s="36" t="s">
+      <c r="E42" s="34" t="s">
         <v>254</v>
       </c>
-      <c r="D42" s="36" t="s">
-        <v>259</v>
-      </c>
-      <c r="E42" s="34" t="s">
-        <v>260</v>
-      </c>
       <c r="F42" s="33" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="G42" s="33" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="H42" s="35" t="n">
         <v>1.2</v>
       </c>
-      <c r="I42" s="35" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J42" s="33"/>
+      <c r="I42" s="33"/>
+      <c r="J42" s="33" t="s">
+        <v>255</v>
+      </c>
       <c r="K42" s="33" t="s">
-        <v>261</v>
-      </c>
-      <c r="L42" s="33" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="36" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="B43" s="36" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="C43" s="36" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="D43" s="36" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="E43" s="34" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="F43" s="33" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="G43" s="33" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="H43" s="35" t="n">
         <v>0.45</v>
       </c>
-      <c r="I43" s="35" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="J43" s="33"/>
+      <c r="I43" s="33"/>
+      <c r="J43" s="33" t="s">
+        <v>259</v>
+      </c>
       <c r="K43" s="33" t="s">
-        <v>265</v>
-      </c>
-      <c r="L43" s="33" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="36" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="B44" s="36" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="C44" s="36" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="D44" s="36" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="E44" s="34" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="F44" s="33" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="G44" s="33" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="H44" s="35" t="n">
         <v>-0.35</v>
       </c>
-      <c r="I44" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" s="33"/>
+      <c r="I44" s="33"/>
+      <c r="J44" s="33" t="s">
+        <v>262</v>
+      </c>
       <c r="K44" s="33" t="s">
-        <v>268</v>
-      </c>
-      <c r="L44" s="33" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="36" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="B45" s="36" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="C45" s="36" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="D45" s="36" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="E45" s="34" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="F45" s="33" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="G45" s="33" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="H45" s="35" t="n">
         <v>-0.25</v>
       </c>
-      <c r="I45" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="J45" s="33"/>
+      <c r="I45" s="33"/>
+      <c r="J45" s="33" t="s">
+        <v>265</v>
+      </c>
       <c r="K45" s="33" t="s">
-        <v>271</v>
-      </c>
-      <c r="L45" s="33" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="36" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="B46" s="36" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="C46" s="36" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="D46" s="36" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="E46" s="34" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="F46" s="33" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="G46" s="33" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="H46" s="35" t="n">
         <v>1.6</v>
       </c>
-      <c r="I46" s="35" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J46" s="33"/>
+      <c r="I46" s="33"/>
+      <c r="J46" s="33" t="s">
+        <v>271</v>
+      </c>
       <c r="K46" s="33" t="s">
-        <v>277</v>
-      </c>
-      <c r="L46" s="33" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="36" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="B47" s="36" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="C47" s="36" t="s">
+        <v>267</v>
+      </c>
+      <c r="D47" s="36" t="s">
         <v>273</v>
       </c>
-      <c r="D47" s="36" t="s">
-        <v>279</v>
-      </c>
       <c r="E47" s="34" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="F47" s="33" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="G47" s="33" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="H47" s="35" t="n">
         <v>1.8</v>
       </c>
-      <c r="I47" s="35" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J47" s="33"/>
+      <c r="I47" s="33"/>
+      <c r="J47" s="33" t="s">
+        <v>275</v>
+      </c>
       <c r="K47" s="33" t="s">
-        <v>281</v>
-      </c>
-      <c r="L47" s="33" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="36" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="B48" s="36" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="C48" s="36" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="D48" s="36" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="E48" s="34" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="F48" s="33" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="G48" s="33" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="H48" s="35" t="n">
         <v>1.3</v>
       </c>
-      <c r="I48" s="35" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J48" s="33"/>
+      <c r="I48" s="33"/>
+      <c r="J48" s="33" t="s">
+        <v>279</v>
+      </c>
       <c r="K48" s="33" t="s">
-        <v>285</v>
-      </c>
-      <c r="L48" s="33" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="36" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="B49" s="36" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="C49" s="36" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="D49" s="36" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="E49" s="34" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="F49" s="33" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="G49" s="33" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="H49" s="35" t="n">
         <v>0.45</v>
       </c>
-      <c r="I49" s="35" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="J49" s="33"/>
+      <c r="I49" s="33"/>
+      <c r="J49" s="33" t="s">
+        <v>282</v>
+      </c>
       <c r="K49" s="33" t="s">
-        <v>288</v>
-      </c>
-      <c r="L49" s="33" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="36" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="B50" s="36" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="C50" s="36" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="D50" s="36" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="E50" s="34" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="F50" s="33" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="G50" s="33" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="H50" s="35" t="n">
         <v>35</v>
       </c>
-      <c r="I50" s="35" t="n">
-        <v>35</v>
-      </c>
-      <c r="J50" s="33"/>
+      <c r="I50" s="33"/>
+      <c r="J50" s="33" t="s">
+        <v>288</v>
+      </c>
       <c r="K50" s="33" t="s">
-        <v>294</v>
-      </c>
-      <c r="L50" s="33" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="36" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="B51" s="36" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="C51" s="36" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="D51" s="36" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="E51" s="34" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="F51" s="33" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="G51" s="33" t="s">
-        <v>300</v>
+        <v>287</v>
       </c>
       <c r="H51" s="35" t="n">
         <v>100</v>
       </c>
-      <c r="I51" s="35" t="n">
-        <v>110</v>
-      </c>
-      <c r="J51" s="33"/>
+      <c r="I51" s="33"/>
+      <c r="J51" s="33" t="s">
+        <v>294</v>
+      </c>
       <c r="K51" s="33" t="s">
-        <v>301</v>
-      </c>
-      <c r="L51" s="33" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="36" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="B52" s="36" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="C52" s="36" t="s">
+        <v>290</v>
+      </c>
+      <c r="D52" s="36" t="s">
         <v>296</v>
       </c>
-      <c r="D52" s="36" t="s">
-        <v>303</v>
-      </c>
       <c r="E52" s="34" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="F52" s="33" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="G52" s="33" t="s">
-        <v>300</v>
+        <v>287</v>
       </c>
       <c r="H52" s="35" t="n">
         <v>130</v>
       </c>
-      <c r="I52" s="35" t="n">
-        <v>145</v>
-      </c>
-      <c r="J52" s="33"/>
+      <c r="I52" s="33"/>
+      <c r="J52" s="33" t="s">
+        <v>52</v>
+      </c>
       <c r="K52" s="33" t="s">
-        <v>54</v>
-      </c>
-      <c r="L52" s="33" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="36" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="B53" s="36" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="C53" s="36" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="D53" s="36" t="s">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="E53" s="34" t="s">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="F53" s="33" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="G53" s="33" t="s">
-        <v>300</v>
+        <v>287</v>
       </c>
       <c r="H53" s="35" t="n">
         <v>170</v>
       </c>
-      <c r="I53" s="35" t="n">
-        <v>183</v>
-      </c>
-      <c r="J53" s="33"/>
+      <c r="I53" s="33"/>
+      <c r="J53" s="33" t="s">
+        <v>301</v>
+      </c>
       <c r="K53" s="33" t="s">
-        <v>308</v>
-      </c>
-      <c r="L53" s="33" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="36" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="B54" s="36" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="C54" s="36" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="D54" s="36" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="E54" s="34" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="F54" s="33" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="G54" s="33" t="s">
-        <v>300</v>
+        <v>287</v>
       </c>
       <c r="H54" s="35" t="n">
         <v>200</v>
       </c>
-      <c r="I54" s="35" t="n">
-        <v>219</v>
-      </c>
-      <c r="J54" s="33"/>
+      <c r="I54" s="33"/>
+      <c r="J54" s="33" t="s">
+        <v>305</v>
+      </c>
       <c r="K54" s="33" t="s">
-        <v>312</v>
-      </c>
-      <c r="L54" s="33" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="36" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="B55" s="36" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="C55" s="36" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="D55" s="36" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="E55" s="34" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="F55" s="33" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="G55" s="33" t="s">
-        <v>300</v>
+        <v>287</v>
       </c>
       <c r="H55" s="35" t="n">
         <v>270</v>
       </c>
-      <c r="I55" s="35" t="n">
-        <v>357</v>
-      </c>
-      <c r="J55" s="33"/>
+      <c r="I55" s="33"/>
+      <c r="J55" s="33" t="s">
+        <v>309</v>
+      </c>
       <c r="K55" s="33" t="s">
-        <v>316</v>
-      </c>
-      <c r="L55" s="33" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="36" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="B56" s="36" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="C56" s="36" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="D56" s="36" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="E56" s="34" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="F56" s="33" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="G56" s="33" t="s">
-        <v>300</v>
+        <v>287</v>
       </c>
       <c r="H56" s="35" t="n">
         <v>340</v>
       </c>
-      <c r="I56" s="35" t="n">
-        <v>450</v>
-      </c>
-      <c r="J56" s="33"/>
+      <c r="I56" s="33"/>
+      <c r="J56" s="33" t="s">
+        <v>313</v>
+      </c>
       <c r="K56" s="33" t="s">
-        <v>320</v>
-      </c>
-      <c r="L56" s="33" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="36" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="B57" s="36" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="C57" s="36" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="D57" s="36" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="E57" s="34" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="F57" s="33" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="G57" s="33" t="s">
-        <v>300</v>
+        <v>287</v>
       </c>
       <c r="H57" s="35" t="n">
         <v>450</v>
       </c>
-      <c r="I57" s="35" t="n">
-        <v>550</v>
-      </c>
-      <c r="J57" s="33"/>
+      <c r="I57" s="33"/>
+      <c r="J57" s="33" t="s">
+        <v>317</v>
+      </c>
       <c r="K57" s="33" t="s">
-        <v>324</v>
-      </c>
-      <c r="L57" s="33" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="36" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="B58" s="36" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="C58" s="36" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="D58" s="36" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="E58" s="34" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="F58" s="33" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="G58" s="33" t="s">
-        <v>300</v>
+        <v>287</v>
       </c>
       <c r="H58" s="35" t="n">
         <v>800</v>
       </c>
-      <c r="I58" s="35" t="n">
-        <v>1080</v>
-      </c>
-      <c r="J58" s="33"/>
+      <c r="I58" s="33"/>
+      <c r="J58" s="33" t="s">
+        <v>321</v>
+      </c>
       <c r="K58" s="33" t="s">
-        <v>328</v>
-      </c>
-      <c r="L58" s="33" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="36" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="B59" s="36" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="C59" s="36" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="D59" s="36" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="E59" s="34" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="F59" s="33" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="G59" s="33" t="s">
-        <v>300</v>
+        <v>287</v>
       </c>
       <c r="H59" s="35" t="n">
         <v>70</v>
       </c>
-      <c r="I59" s="35" t="n">
-        <v>90</v>
-      </c>
-      <c r="J59" s="33"/>
+      <c r="I59" s="33"/>
+      <c r="J59" s="33" t="s">
+        <v>325</v>
+      </c>
       <c r="K59" s="33" t="s">
-        <v>332</v>
-      </c>
-      <c r="L59" s="33" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="36" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="B60" s="36" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="C60" s="36" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="D60" s="36" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="E60" s="34" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="F60" s="33" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="G60" s="33" t="s">
-        <v>300</v>
+        <v>287</v>
       </c>
       <c r="H60" s="35" t="n">
         <v>70</v>
       </c>
-      <c r="I60" s="35" t="n">
-        <v>90</v>
-      </c>
-      <c r="J60" s="33"/>
+      <c r="I60" s="33"/>
+      <c r="J60" s="33" t="s">
+        <v>329</v>
+      </c>
       <c r="K60" s="33" t="s">
-        <v>336</v>
-      </c>
-      <c r="L60" s="33" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="36" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="B61" s="36" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="C61" s="36" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="D61" s="36" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="E61" s="34" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="F61" s="33" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="G61" s="33" t="s">
-        <v>300</v>
+        <v>287</v>
       </c>
       <c r="H61" s="35" t="n">
         <v>80</v>
       </c>
-      <c r="I61" s="35" t="n">
-        <v>90</v>
-      </c>
-      <c r="J61" s="33"/>
+      <c r="I61" s="33"/>
+      <c r="J61" s="33" t="s">
+        <v>335</v>
+      </c>
       <c r="K61" s="33" t="s">
-        <v>342</v>
-      </c>
-      <c r="L61" s="33" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="36" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="B62" s="36" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="C62" s="36" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="D62" s="36" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="E62" s="34" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="F62" s="33" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="G62" s="33" t="s">
-        <v>300</v>
+        <v>287</v>
       </c>
       <c r="H62" s="35" t="n">
         <v>90</v>
       </c>
-      <c r="I62" s="35" t="n">
-        <v>110</v>
-      </c>
-      <c r="J62" s="33"/>
+      <c r="I62" s="33"/>
+      <c r="J62" s="33" t="s">
+        <v>338</v>
+      </c>
       <c r="K62" s="33" t="s">
-        <v>345</v>
-      </c>
-      <c r="L62" s="33" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="36" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="B63" s="36" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="C63" s="36" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="D63" s="36" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="E63" s="34" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="F63" s="33" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="G63" s="33" t="s">
-        <v>300</v>
+        <v>287</v>
       </c>
       <c r="H63" s="35" t="n">
         <v>120</v>
       </c>
-      <c r="I63" s="35" t="n">
-        <v>145</v>
-      </c>
-      <c r="J63" s="33"/>
+      <c r="I63" s="33"/>
+      <c r="J63" s="33" t="s">
+        <v>341</v>
+      </c>
       <c r="K63" s="33" t="s">
-        <v>348</v>
-      </c>
-      <c r="L63" s="33" t="s">
-        <v>349</v>
+        <v>342</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="36" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="B64" s="36" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="C64" s="36" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="D64" s="36" t="s">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="E64" s="34" t="s">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="F64" s="33" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="G64" s="33" t="s">
-        <v>300</v>
+        <v>287</v>
       </c>
       <c r="H64" s="35" t="n">
         <v>150</v>
       </c>
-      <c r="I64" s="35" t="n">
-        <v>183</v>
-      </c>
-      <c r="J64" s="33"/>
+      <c r="I64" s="33"/>
+      <c r="J64" s="33" t="s">
+        <v>344</v>
+      </c>
       <c r="K64" s="33" t="s">
-        <v>351</v>
-      </c>
-      <c r="L64" s="33" t="s">
-        <v>352</v>
+        <v>345</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="36" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="B65" s="36" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="C65" s="36" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="D65" s="36" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="E65" s="34" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="F65" s="33" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="G65" s="33" t="s">
-        <v>300</v>
+        <v>287</v>
       </c>
       <c r="H65" s="35" t="n">
         <v>180</v>
       </c>
-      <c r="I65" s="35" t="n">
-        <v>219</v>
-      </c>
-      <c r="J65" s="33"/>
+      <c r="I65" s="33"/>
+      <c r="J65" s="33" t="s">
+        <v>347</v>
+      </c>
       <c r="K65" s="33" t="s">
-        <v>354</v>
-      </c>
-      <c r="L65" s="33" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="36" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="B66" s="36" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="C66" s="36" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="D66" s="36" t="s">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="E66" s="34" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="F66" s="33" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="G66" s="33" t="s">
-        <v>300</v>
+        <v>287</v>
       </c>
       <c r="H66" s="35" t="n">
         <v>240</v>
       </c>
-      <c r="I66" s="35" t="n">
-        <v>357</v>
-      </c>
-      <c r="J66" s="33"/>
+      <c r="I66" s="33"/>
+      <c r="J66" s="33" t="s">
+        <v>350</v>
+      </c>
       <c r="K66" s="33" t="s">
-        <v>357</v>
-      </c>
-      <c r="L66" s="33" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="36" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="B67" s="36" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="C67" s="36" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="D67" s="36" t="s">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="E67" s="34" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="F67" s="33" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="G67" s="33" t="s">
-        <v>300</v>
+        <v>287</v>
       </c>
       <c r="H67" s="35" t="n">
         <v>320</v>
       </c>
-      <c r="I67" s="35" t="n">
-        <v>450</v>
-      </c>
-      <c r="J67" s="33"/>
+      <c r="I67" s="33"/>
+      <c r="J67" s="33" t="s">
+        <v>353</v>
+      </c>
       <c r="K67" s="33" t="s">
-        <v>360</v>
-      </c>
-      <c r="L67" s="33" t="s">
-        <v>361</v>
+        <v>354</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="36" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="B68" s="36" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="C68" s="36" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="D68" s="36" t="s">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="E68" s="34" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="F68" s="33" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="G68" s="33" t="s">
-        <v>300</v>
+        <v>287</v>
       </c>
       <c r="H68" s="35" t="n">
         <v>500</v>
       </c>
-      <c r="I68" s="35" t="n">
-        <v>550</v>
-      </c>
-      <c r="J68" s="33"/>
+      <c r="I68" s="33"/>
+      <c r="J68" s="33" t="s">
+        <v>356</v>
+      </c>
       <c r="K68" s="33" t="s">
-        <v>363</v>
-      </c>
-      <c r="L68" s="33" t="s">
-        <v>364</v>
+        <v>357</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="36" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="B69" s="36" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="C69" s="36" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="D69" s="36" t="s">
-        <v>365</v>
+        <v>358</v>
       </c>
       <c r="E69" s="34" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="F69" s="33" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="G69" s="33" t="s">
-        <v>300</v>
+        <v>287</v>
       </c>
       <c r="H69" s="35" t="n">
         <v>100</v>
       </c>
-      <c r="I69" s="35" t="n">
-        <v>100</v>
-      </c>
-      <c r="J69" s="33"/>
+      <c r="I69" s="33"/>
+      <c r="J69" s="33" t="s">
+        <v>360</v>
+      </c>
       <c r="K69" s="33" t="s">
-        <v>367</v>
-      </c>
-      <c r="L69" s="33" t="s">
-        <v>368</v>
+        <v>361</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="36" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="B70" s="36" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="C70" s="36" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="D70" s="36" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="E70" s="34" t="s">
-        <v>370</v>
+        <v>363</v>
       </c>
       <c r="F70" s="33" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="G70" s="33" t="s">
-        <v>300</v>
+        <v>287</v>
       </c>
       <c r="H70" s="35" t="n">
         <v>100</v>
       </c>
-      <c r="I70" s="35" t="n">
-        <v>100</v>
-      </c>
-      <c r="J70" s="33"/>
+      <c r="I70" s="33"/>
+      <c r="J70" s="33" t="s">
+        <v>364</v>
+      </c>
       <c r="K70" s="33" t="s">
-        <v>371</v>
-      </c>
-      <c r="L70" s="33" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="36" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="B71" s="36" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="C71" s="36" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="D71" s="36" t="s">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="E71" s="34" t="s">
-        <v>375</v>
+        <v>368</v>
       </c>
       <c r="F71" s="33" t="s">
-        <v>376</v>
+        <v>369</v>
       </c>
       <c r="G71" s="33" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="H71" s="35" t="n">
         <v>65</v>
       </c>
-      <c r="I71" s="35" t="n">
-        <v>65</v>
-      </c>
-      <c r="J71" s="33"/>
+      <c r="I71" s="33"/>
+      <c r="J71" s="33" t="s">
+        <v>370</v>
+      </c>
       <c r="K71" s="33" t="s">
-        <v>377</v>
-      </c>
-      <c r="L71" s="33" t="s">
-        <v>378</v>
+        <v>371</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="36" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="B72" s="36" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="C72" s="36" t="s">
+        <v>366</v>
+      </c>
+      <c r="D72" s="36" t="s">
+        <v>372</v>
+      </c>
+      <c r="E72" s="34" t="s">
         <v>373</v>
       </c>
-      <c r="D72" s="36" t="s">
-        <v>379</v>
-      </c>
-      <c r="E72" s="34" t="s">
-        <v>380</v>
-      </c>
       <c r="F72" s="33" t="s">
-        <v>376</v>
+        <v>369</v>
       </c>
       <c r="G72" s="33" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="H72" s="35" t="n">
         <v>60</v>
       </c>
-      <c r="I72" s="35" t="n">
-        <v>60</v>
-      </c>
-      <c r="J72" s="33"/>
+      <c r="I72" s="33"/>
+      <c r="J72" s="33" t="s">
+        <v>374</v>
+      </c>
       <c r="K72" s="33" t="s">
-        <v>381</v>
-      </c>
-      <c r="L72" s="33" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="36" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="B73" s="36" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="C73" s="36" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="D73" s="36" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="E73" s="34" t="s">
-        <v>384</v>
+        <v>377</v>
       </c>
       <c r="F73" s="33" t="s">
-        <v>376</v>
+        <v>369</v>
       </c>
       <c r="G73" s="33" t="s">
-        <v>385</v>
+        <v>236</v>
       </c>
       <c r="H73" s="35" t="n">
         <v>90</v>
       </c>
-      <c r="I73" s="35" t="n">
-        <v>90</v>
+      <c r="I73" s="33" t="s">
+        <v>378</v>
       </c>
       <c r="J73" s="33" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="K73" s="33" t="s">
-        <v>387</v>
-      </c>
-      <c r="L73" s="33" t="s">
-        <v>388</v>
+        <v>380</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="36" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="B74" s="36" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="C74" s="36" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="D74" s="36" t="s">
-        <v>389</v>
+        <v>381</v>
       </c>
       <c r="E74" s="34" t="s">
-        <v>390</v>
+        <v>382</v>
       </c>
       <c r="F74" s="33" t="s">
-        <v>376</v>
+        <v>369</v>
       </c>
       <c r="G74" s="33" t="s">
-        <v>385</v>
+        <v>236</v>
       </c>
       <c r="H74" s="35" t="n">
         <v>90</v>
       </c>
-      <c r="I74" s="35" t="n">
-        <v>90</v>
+      <c r="I74" s="33" t="s">
+        <v>378</v>
       </c>
       <c r="J74" s="33" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="K74" s="33" t="s">
-        <v>391</v>
-      </c>
-      <c r="L74" s="33" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="36" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="B75" s="36" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="C75" s="36" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="D75" s="36" t="s">
-        <v>393</v>
+        <v>385</v>
       </c>
       <c r="E75" s="34" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="F75" s="33" t="s">
-        <v>376</v>
+        <v>369</v>
       </c>
       <c r="G75" s="33" t="s">
-        <v>385</v>
+        <v>236</v>
       </c>
       <c r="H75" s="35" t="n">
         <v>90</v>
       </c>
-      <c r="I75" s="35" t="n">
-        <v>90</v>
+      <c r="I75" s="33" t="s">
+        <v>378</v>
       </c>
       <c r="J75" s="33" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="K75" s="33" t="s">
-        <v>395</v>
-      </c>
-      <c r="L75" s="33" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="36" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="B76" s="36" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="C76" s="36" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="D76" s="36" t="s">
-        <v>397</v>
+        <v>389</v>
       </c>
       <c r="E76" s="34" t="s">
-        <v>398</v>
+        <v>390</v>
       </c>
       <c r="F76" s="33" t="s">
-        <v>376</v>
+        <v>369</v>
       </c>
       <c r="G76" s="33" t="s">
-        <v>385</v>
+        <v>236</v>
       </c>
       <c r="H76" s="35" t="n">
         <v>90</v>
       </c>
-      <c r="I76" s="35" t="n">
-        <v>90</v>
+      <c r="I76" s="33" t="s">
+        <v>378</v>
       </c>
       <c r="J76" s="33" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="K76" s="33" t="s">
-        <v>399</v>
-      </c>
-      <c r="L76" s="33" t="s">
-        <v>400</v>
+        <v>392</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="36" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="B77" s="36" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="C77" s="36" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="D77" s="36" t="s">
-        <v>401</v>
+        <v>393</v>
       </c>
       <c r="E77" s="34" t="s">
-        <v>402</v>
+        <v>394</v>
       </c>
       <c r="F77" s="33" t="s">
-        <v>376</v>
+        <v>369</v>
       </c>
       <c r="G77" s="33" t="s">
-        <v>385</v>
+        <v>236</v>
       </c>
       <c r="H77" s="35" t="n">
         <v>90</v>
       </c>
-      <c r="I77" s="35" t="n">
-        <v>90</v>
+      <c r="I77" s="33" t="s">
+        <v>378</v>
       </c>
       <c r="J77" s="33" t="s">
-        <v>386</v>
+        <v>395</v>
       </c>
       <c r="K77" s="33" t="s">
-        <v>403</v>
-      </c>
-      <c r="L77" s="33" t="s">
-        <v>404</v>
+        <v>396</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="36" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="B78" s="36" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="C78" s="36" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="D78" s="36" t="s">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="E78" s="34" t="s">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="F78" s="33" t="s">
-        <v>376</v>
+        <v>369</v>
       </c>
       <c r="G78" s="33" t="s">
-        <v>385</v>
+        <v>236</v>
       </c>
       <c r="H78" s="35" t="n">
         <v>30</v>
       </c>
-      <c r="I78" s="35" t="n">
-        <v>30</v>
+      <c r="I78" s="33" t="s">
+        <v>378</v>
       </c>
       <c r="J78" s="33" t="s">
-        <v>386</v>
+        <v>399</v>
       </c>
       <c r="K78" s="33" t="s">
-        <v>407</v>
-      </c>
-      <c r="L78" s="33" t="s">
-        <v>408</v>
+        <v>400</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="36" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="B79" s="36" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="C79" s="36" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="D79" s="36" t="s">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="E79" s="34" t="s">
-        <v>410</v>
+        <v>402</v>
       </c>
       <c r="F79" s="33" t="s">
-        <v>376</v>
+        <v>369</v>
       </c>
       <c r="G79" s="33" t="s">
-        <v>385</v>
+        <v>236</v>
       </c>
       <c r="H79" s="35" t="n">
         <v>90</v>
       </c>
-      <c r="I79" s="35" t="n">
-        <v>90</v>
+      <c r="I79" s="33" t="s">
+        <v>378</v>
       </c>
       <c r="J79" s="33" t="s">
-        <v>386</v>
+        <v>403</v>
       </c>
       <c r="K79" s="33" t="s">
-        <v>411</v>
-      </c>
-      <c r="L79" s="33" t="s">
-        <v>412</v>
+        <v>404</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="36" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="B80" s="36" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="C80" s="36" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="D80" s="36" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="E80" s="34" t="s">
-        <v>414</v>
+        <v>406</v>
       </c>
       <c r="F80" s="33" t="s">
-        <v>376</v>
+        <v>369</v>
       </c>
       <c r="G80" s="33" t="s">
-        <v>385</v>
+        <v>236</v>
       </c>
       <c r="H80" s="35" t="n">
         <v>90</v>
       </c>
-      <c r="I80" s="35" t="n">
-        <v>90</v>
+      <c r="I80" s="33" t="s">
+        <v>378</v>
       </c>
       <c r="J80" s="33" t="s">
-        <v>386</v>
+        <v>407</v>
       </c>
       <c r="K80" s="33" t="s">
-        <v>415</v>
-      </c>
-      <c r="L80" s="33" t="s">
-        <v>416</v>
+        <v>408</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="36" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="B81" s="36" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="C81" s="36" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="D81" s="36" t="s">
-        <v>417</v>
+        <v>409</v>
       </c>
       <c r="E81" s="34" t="s">
-        <v>418</v>
+        <v>410</v>
       </c>
       <c r="F81" s="33" t="s">
-        <v>376</v>
+        <v>369</v>
       </c>
       <c r="G81" s="33" t="s">
-        <v>385</v>
+        <v>236</v>
       </c>
       <c r="H81" s="35" t="n">
         <v>90</v>
       </c>
-      <c r="I81" s="35" t="n">
-        <v>90</v>
+      <c r="I81" s="33" t="s">
+        <v>378</v>
       </c>
       <c r="J81" s="33" t="s">
-        <v>386</v>
+        <v>411</v>
       </c>
       <c r="K81" s="33" t="s">
-        <v>419</v>
-      </c>
-      <c r="L81" s="33" t="s">
-        <v>420</v>
+        <v>412</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="36" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="B82" s="36" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="C82" s="36" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="D82" s="36" t="s">
-        <v>421</v>
+        <v>413</v>
       </c>
       <c r="E82" s="34" t="s">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="F82" s="33" t="s">
-        <v>376</v>
+        <v>369</v>
       </c>
       <c r="G82" s="33" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="H82" s="35" t="n">
         <v>80</v>
       </c>
-      <c r="I82" s="35" t="n">
-        <v>80</v>
-      </c>
-      <c r="J82" s="33"/>
+      <c r="I82" s="33"/>
+      <c r="J82" s="33" t="s">
+        <v>415</v>
+      </c>
       <c r="K82" s="33" t="s">
-        <v>423</v>
-      </c>
-      <c r="L82" s="33" t="s">
-        <v>424</v>
+        <v>416</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="36" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="B83" s="36" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="C83" s="36" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="D83" s="36" t="s">
-        <v>425</v>
+        <v>417</v>
       </c>
       <c r="E83" s="34" t="s">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="F83" s="33" t="s">
-        <v>376</v>
+        <v>369</v>
       </c>
       <c r="G83" s="33" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="H83" s="35" t="n">
         <v>40</v>
       </c>
-      <c r="I83" s="35" t="n">
-        <v>40</v>
-      </c>
-      <c r="J83" s="33"/>
+      <c r="I83" s="33"/>
+      <c r="J83" s="33" t="s">
+        <v>419</v>
+      </c>
       <c r="K83" s="33" t="s">
-        <v>427</v>
-      </c>
-      <c r="L83" s="33" t="s">
-        <v>428</v>
+        <v>420</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="36" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="B84" s="36" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="C84" s="36" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="D84" s="36" t="s">
-        <v>429</v>
+        <v>421</v>
       </c>
       <c r="E84" s="34" t="s">
-        <v>430</v>
+        <v>422</v>
       </c>
       <c r="F84" s="33" t="s">
-        <v>376</v>
+        <v>369</v>
       </c>
       <c r="G84" s="33" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="H84" s="35" t="n">
         <v>60</v>
       </c>
-      <c r="I84" s="35" t="n">
-        <v>60</v>
-      </c>
-      <c r="J84" s="33"/>
+      <c r="I84" s="33"/>
+      <c r="J84" s="33" t="s">
+        <v>423</v>
+      </c>
       <c r="K84" s="33" t="s">
-        <v>431</v>
-      </c>
-      <c r="L84" s="33" t="s">
-        <v>432</v>
+        <v>424</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="36" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="B85" s="36" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="C85" s="36" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="D85" s="36" t="s">
-        <v>433</v>
+        <v>425</v>
       </c>
       <c r="E85" s="34" t="s">
-        <v>434</v>
+        <v>426</v>
       </c>
       <c r="F85" s="33" t="s">
-        <v>376</v>
+        <v>369</v>
       </c>
       <c r="G85" s="33" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="H85" s="35" t="n">
         <v>50</v>
       </c>
-      <c r="I85" s="35" t="n">
-        <v>50</v>
-      </c>
-      <c r="J85" s="33"/>
+      <c r="I85" s="33"/>
+      <c r="J85" s="33" t="s">
+        <v>427</v>
+      </c>
       <c r="K85" s="33" t="s">
-        <v>435</v>
-      </c>
-      <c r="L85" s="33" t="s">
-        <v>436</v>
+        <v>428</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="36" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="B86" s="36" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="C86" s="36" t="s">
-        <v>437</v>
+        <v>429</v>
       </c>
       <c r="D86" s="36" t="s">
-        <v>438</v>
+        <v>430</v>
       </c>
       <c r="E86" s="34" t="s">
-        <v>439</v>
+        <v>431</v>
       </c>
       <c r="F86" s="33" t="s">
-        <v>440</v>
+        <v>432</v>
       </c>
       <c r="G86" s="33" t="s">
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="H86" s="35" t="n">
         <v>300</v>
       </c>
-      <c r="I86" s="35" t="n">
-        <v>350</v>
-      </c>
-      <c r="J86" s="33"/>
+      <c r="I86" s="33"/>
+      <c r="J86" s="33" t="s">
+        <v>434</v>
+      </c>
       <c r="K86" s="33" t="s">
-        <v>442</v>
-      </c>
-      <c r="L86" s="33" t="s">
-        <v>443</v>
+        <v>435</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="36" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="B87" s="36" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="C87" s="36" t="s">
+        <v>429</v>
+      </c>
+      <c r="D87" s="36" t="s">
+        <v>436</v>
+      </c>
+      <c r="E87" s="34" t="s">
         <v>437</v>
       </c>
-      <c r="D87" s="36" t="s">
-        <v>444</v>
-      </c>
-      <c r="E87" s="34" t="s">
-        <v>445</v>
-      </c>
       <c r="F87" s="33" t="s">
-        <v>446</v>
+        <v>438</v>
       </c>
       <c r="G87" s="33" t="s">
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="H87" s="35" t="n">
         <v>250</v>
       </c>
-      <c r="I87" s="35" t="n">
-        <v>300</v>
-      </c>
-      <c r="J87" s="33"/>
+      <c r="I87" s="33"/>
+      <c r="J87" s="33" t="s">
+        <v>439</v>
+      </c>
       <c r="K87" s="33" t="s">
-        <v>447</v>
-      </c>
-      <c r="L87" s="33" t="s">
-        <v>448</v>
+        <v>440</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="36" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="B88" s="36" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="C88" s="36" t="s">
-        <v>437</v>
+        <v>429</v>
       </c>
       <c r="D88" s="36" t="s">
-        <v>449</v>
+        <v>441</v>
       </c>
       <c r="E88" s="34" t="s">
-        <v>450</v>
+        <v>442</v>
       </c>
       <c r="F88" s="33"/>
       <c r="G88" s="33" t="s">
-        <v>242</v>
+        <v>287</v>
       </c>
       <c r="H88" s="35" t="n">
         <v>80</v>
       </c>
-      <c r="I88" s="35" t="n">
-        <v>80</v>
-      </c>
-      <c r="J88" s="33"/>
+      <c r="I88" s="33"/>
+      <c r="J88" s="33" t="s">
+        <v>443</v>
+      </c>
       <c r="K88" s="33" t="s">
-        <v>451</v>
-      </c>
-      <c r="L88" s="33" t="s">
-        <v>452</v>
+        <v>444</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="36" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="B89" s="36" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="C89" s="36" t="s">
-        <v>437</v>
+        <v>429</v>
       </c>
       <c r="D89" s="36" t="s">
-        <v>453</v>
+        <v>445</v>
       </c>
       <c r="E89" s="34" t="s">
-        <v>454</v>
+        <v>446</v>
       </c>
       <c r="F89" s="33"/>
       <c r="G89" s="33" t="s">
-        <v>242</v>
+        <v>287</v>
       </c>
       <c r="H89" s="35" t="n">
         <v>50</v>
       </c>
-      <c r="I89" s="35" t="n">
-        <v>50</v>
-      </c>
-      <c r="J89" s="33"/>
+      <c r="I89" s="33"/>
+      <c r="J89" s="33" t="s">
+        <v>447</v>
+      </c>
       <c r="K89" s="33" t="s">
-        <v>455</v>
-      </c>
-      <c r="L89" s="33" t="s">
-        <v>456</v>
+        <v>448</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="36" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="B90" s="36" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="C90" s="36" t="s">
-        <v>457</v>
+        <v>449</v>
       </c>
       <c r="D90" s="36" t="s">
-        <v>458</v>
+        <v>450</v>
       </c>
       <c r="E90" s="34" t="s">
-        <v>459</v>
+        <v>451</v>
       </c>
       <c r="F90" s="33"/>
       <c r="G90" s="33" t="s">
-        <v>460</v>
+        <v>452</v>
       </c>
       <c r="H90" s="35" t="n">
         <v>5</v>
       </c>
-      <c r="I90" s="35" t="n">
-        <v>7</v>
-      </c>
-      <c r="J90" s="33"/>
+      <c r="I90" s="33" t="s">
+        <v>453</v>
+      </c>
+      <c r="J90" s="33" t="s">
+        <v>454</v>
+      </c>
       <c r="K90" s="33" t="s">
-        <v>461</v>
-      </c>
-      <c r="L90" s="33" t="s">
-        <v>462</v>
+        <v>455</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="36" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="B91" s="36" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="C91" s="36" t="s">
+        <v>449</v>
+      </c>
+      <c r="D91" s="36" t="s">
+        <v>456</v>
+      </c>
+      <c r="E91" s="34" t="s">
         <v>457</v>
-      </c>
-      <c r="D91" s="36" t="s">
-        <v>463</v>
-      </c>
-      <c r="E91" s="34" t="s">
-        <v>464</v>
       </c>
       <c r="F91" s="33"/>
       <c r="G91" s="33" t="s">
-        <v>460</v>
+        <v>452</v>
       </c>
       <c r="H91" s="35" t="n">
         <v>3.5</v>
       </c>
-      <c r="I91" s="35" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J91" s="33"/>
+      <c r="I91" s="33" t="s">
+        <v>453</v>
+      </c>
+      <c r="J91" s="33" t="s">
+        <v>458</v>
+      </c>
       <c r="K91" s="33" t="s">
-        <v>465</v>
-      </c>
-      <c r="L91" s="33" t="s">
-        <v>466</v>
+        <v>459</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="36" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="B92" s="36" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="C92" s="36" t="s">
-        <v>467</v>
+        <v>460</v>
       </c>
       <c r="D92" s="36" t="s">
-        <v>468</v>
+        <v>461</v>
       </c>
       <c r="E92" s="34" t="s">
-        <v>469</v>
+        <v>462</v>
       </c>
       <c r="F92" s="33"/>
       <c r="G92" s="33" t="s">
-        <v>460</v>
+        <v>452</v>
       </c>
       <c r="H92" s="35" t="n">
         <v>4.5</v>
       </c>
-      <c r="I92" s="35" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J92" s="33"/>
+      <c r="I92" s="33" t="s">
+        <v>453</v>
+      </c>
+      <c r="J92" s="33" t="s">
+        <v>53</v>
+      </c>
       <c r="K92" s="33" t="s">
-        <v>55</v>
-      </c>
-      <c r="L92" s="33" t="s">
-        <v>470</v>
+        <v>463</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="36" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="B93" s="36" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="C93" s="36" t="s">
-        <v>467</v>
+        <v>460</v>
       </c>
       <c r="D93" s="36" t="s">
-        <v>471</v>
+        <v>464</v>
       </c>
       <c r="E93" s="34" t="s">
-        <v>472</v>
+        <v>465</v>
       </c>
       <c r="F93" s="33"/>
       <c r="G93" s="33" t="s">
-        <v>460</v>
+        <v>452</v>
       </c>
       <c r="H93" s="35" t="n">
         <v>4</v>
       </c>
-      <c r="I93" s="35" t="n">
-        <v>4</v>
-      </c>
-      <c r="J93" s="33"/>
+      <c r="I93" s="33" t="s">
+        <v>453</v>
+      </c>
+      <c r="J93" s="33" t="s">
+        <v>466</v>
+      </c>
       <c r="K93" s="33" t="s">
-        <v>473</v>
-      </c>
-      <c r="L93" s="33" t="s">
-        <v>474</v>
+        <v>467</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="36" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="B94" s="36" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="C94" s="36" t="s">
-        <v>467</v>
+        <v>460</v>
       </c>
       <c r="D94" s="36" t="s">
-        <v>475</v>
+        <v>468</v>
       </c>
       <c r="E94" s="34" t="s">
-        <v>476</v>
+        <v>469</v>
       </c>
       <c r="F94" s="33"/>
       <c r="G94" s="33" t="s">
-        <v>460</v>
+        <v>452</v>
       </c>
       <c r="H94" s="35" t="n">
         <v>3.5</v>
       </c>
-      <c r="I94" s="35" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J94" s="33"/>
+      <c r="I94" s="33" t="s">
+        <v>453</v>
+      </c>
+      <c r="J94" s="33" t="s">
+        <v>470</v>
+      </c>
       <c r="K94" s="33" t="s">
-        <v>477</v>
-      </c>
-      <c r="L94" s="33" t="s">
-        <v>478</v>
+        <v>471</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="36" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="B95" s="36" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="C95" s="36" t="s">
-        <v>467</v>
+        <v>460</v>
       </c>
       <c r="D95" s="36" t="s">
-        <v>479</v>
+        <v>472</v>
       </c>
       <c r="E95" s="34" t="s">
-        <v>480</v>
+        <v>473</v>
       </c>
       <c r="F95" s="33"/>
       <c r="G95" s="33" t="s">
-        <v>460</v>
+        <v>452</v>
       </c>
       <c r="H95" s="35" t="n">
         <v>3.3</v>
       </c>
-      <c r="I95" s="35" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J95" s="33"/>
+      <c r="I95" s="33" t="s">
+        <v>453</v>
+      </c>
+      <c r="J95" s="33" t="s">
+        <v>474</v>
+      </c>
       <c r="K95" s="33" t="s">
-        <v>481</v>
-      </c>
-      <c r="L95" s="33" t="s">
-        <v>482</v>
+        <v>475</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="36" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="B96" s="36" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="C96" s="36" t="s">
-        <v>483</v>
+        <v>476</v>
       </c>
       <c r="D96" s="36" t="s">
-        <v>484</v>
+        <v>477</v>
       </c>
       <c r="E96" s="34" t="s">
-        <v>485</v>
+        <v>478</v>
       </c>
       <c r="F96" s="33"/>
       <c r="G96" s="33" t="s">
-        <v>242</v>
+        <v>287</v>
       </c>
       <c r="H96" s="35" t="n">
         <v>3</v>
       </c>
-      <c r="I96" s="35" t="n">
-        <v>3</v>
-      </c>
-      <c r="J96" s="33"/>
+      <c r="I96" s="33"/>
+      <c r="J96" s="33" t="s">
+        <v>479</v>
+      </c>
       <c r="K96" s="33" t="s">
-        <v>486</v>
-      </c>
-      <c r="L96" s="33" t="s">
-        <v>487</v>
+        <v>480</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="36" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="B97" s="36" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="C97" s="36" t="s">
-        <v>483</v>
+        <v>476</v>
       </c>
       <c r="D97" s="36" t="s">
-        <v>488</v>
+        <v>481</v>
       </c>
       <c r="E97" s="34" t="s">
-        <v>489</v>
+        <v>482</v>
       </c>
       <c r="F97" s="33"/>
       <c r="G97" s="33" t="s">
-        <v>242</v>
+        <v>287</v>
       </c>
       <c r="H97" s="35" t="n">
         <v>3</v>
       </c>
-      <c r="I97" s="35" t="n">
-        <v>3</v>
-      </c>
-      <c r="J97" s="33"/>
+      <c r="I97" s="33"/>
+      <c r="J97" s="33" t="s">
+        <v>483</v>
+      </c>
       <c r="K97" s="33" t="s">
-        <v>490</v>
-      </c>
-      <c r="L97" s="33" t="s">
-        <v>491</v>
+        <v>484</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="36" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="B98" s="36" t="s">
-        <v>492</v>
+        <v>485</v>
       </c>
       <c r="C98" s="36" t="s">
-        <v>492</v>
+        <v>485</v>
       </c>
       <c r="D98" s="36" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="E98" s="34" t="s">
-        <v>494</v>
+        <v>487</v>
       </c>
       <c r="F98" s="33"/>
       <c r="G98" s="33" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="H98" s="35" t="n">
         <v>2.4</v>
       </c>
-      <c r="I98" s="35" t="n">
-        <v>3</v>
-      </c>
-      <c r="J98" s="33"/>
+      <c r="I98" s="33"/>
+      <c r="J98" s="33" t="s">
+        <v>488</v>
+      </c>
       <c r="K98" s="33" t="s">
-        <v>495</v>
-      </c>
-      <c r="L98" s="33" t="s">
-        <v>496</v>
+        <v>489</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="36" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="B99" s="36" t="s">
-        <v>492</v>
+        <v>485</v>
       </c>
       <c r="C99" s="36" t="s">
-        <v>492</v>
+        <v>485</v>
       </c>
       <c r="D99" s="36" t="s">
-        <v>497</v>
+        <v>490</v>
       </c>
       <c r="E99" s="34" t="s">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="F99" s="33"/>
       <c r="G99" s="33" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="H99" s="35" t="n">
         <v>2.4</v>
       </c>
-      <c r="I99" s="35" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="J99" s="33"/>
+      <c r="I99" s="33"/>
+      <c r="J99" s="33" t="s">
+        <v>492</v>
+      </c>
       <c r="K99" s="33" t="s">
-        <v>499</v>
-      </c>
-      <c r="L99" s="33" t="s">
-        <v>500</v>
+        <v>493</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="36" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="B100" s="36" t="s">
-        <v>492</v>
+        <v>485</v>
       </c>
       <c r="C100" s="36" t="s">
-        <v>492</v>
+        <v>485</v>
       </c>
       <c r="D100" s="36" t="s">
-        <v>501</v>
+        <v>494</v>
       </c>
       <c r="E100" s="34" t="s">
-        <v>502</v>
+        <v>495</v>
       </c>
       <c r="F100" s="33"/>
       <c r="G100" s="33" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="H100" s="35" t="n">
         <v>3</v>
       </c>
-      <c r="I100" s="35" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="J100" s="33"/>
+      <c r="I100" s="33"/>
+      <c r="J100" s="33" t="s">
+        <v>496</v>
+      </c>
       <c r="K100" s="33" t="s">
-        <v>503</v>
-      </c>
-      <c r="L100" s="33" t="s">
-        <v>504</v>
+        <v>497</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="36" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="B101" s="36" t="s">
-        <v>505</v>
+        <v>498</v>
       </c>
       <c r="C101" s="36" t="s">
-        <v>505</v>
+        <v>498</v>
       </c>
       <c r="D101" s="36" t="s">
-        <v>506</v>
+        <v>499</v>
       </c>
       <c r="E101" s="34" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="F101" s="33"/>
       <c r="G101" s="33" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="H101" s="35" t="n">
         <v>2.4</v>
       </c>
-      <c r="I101" s="35" t="n">
-        <v>3</v>
-      </c>
-      <c r="J101" s="33"/>
+      <c r="I101" s="33"/>
+      <c r="J101" s="33" t="s">
+        <v>501</v>
+      </c>
       <c r="K101" s="33" t="s">
-        <v>508</v>
-      </c>
-      <c r="L101" s="33" t="s">
-        <v>509</v>
+        <v>502</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="36" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="B102" s="36" t="s">
-        <v>505</v>
+        <v>498</v>
       </c>
       <c r="C102" s="36" t="s">
-        <v>505</v>
+        <v>498</v>
       </c>
       <c r="D102" s="36" t="s">
-        <v>510</v>
+        <v>503</v>
       </c>
       <c r="E102" s="34" t="s">
-        <v>511</v>
+        <v>504</v>
       </c>
       <c r="F102" s="33"/>
       <c r="G102" s="33" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="H102" s="35" t="n">
         <v>2.4</v>
       </c>
-      <c r="I102" s="35" t="n">
-        <v>3</v>
-      </c>
-      <c r="J102" s="33"/>
+      <c r="I102" s="33"/>
+      <c r="J102" s="33" t="s">
+        <v>505</v>
+      </c>
       <c r="K102" s="33" t="s">
-        <v>512</v>
-      </c>
-      <c r="L102" s="33" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="36" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="B103" s="36" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="C103" s="36" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="D103" s="36" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="E103" s="34" t="s">
-        <v>516</v>
+        <v>509</v>
       </c>
       <c r="F103" s="33" t="s">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="G103" s="33" t="s">
-        <v>104</v>
+        <v>433</v>
       </c>
       <c r="H103" s="35" t="n">
         <v>65</v>
       </c>
-      <c r="I103" s="35" t="n">
-        <v>80</v>
-      </c>
-      <c r="J103" s="33"/>
+      <c r="I103" s="33"/>
+      <c r="J103" s="33" t="s">
+        <v>511</v>
+      </c>
       <c r="K103" s="33" t="s">
-        <v>518</v>
-      </c>
-      <c r="L103" s="33" t="s">
-        <v>519</v>
+        <v>512</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="36" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="B104" s="36" t="s">
+        <v>507</v>
+      </c>
+      <c r="C104" s="36" t="s">
+        <v>507</v>
+      </c>
+      <c r="D104" s="36" t="s">
+        <v>513</v>
+      </c>
+      <c r="E104" s="34" t="s">
         <v>514</v>
       </c>
-      <c r="C104" s="36" t="s">
-        <v>514</v>
-      </c>
-      <c r="D104" s="36" t="s">
-        <v>520</v>
-      </c>
-      <c r="E104" s="34" t="s">
-        <v>521</v>
-      </c>
       <c r="F104" s="33" t="s">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="G104" s="33" t="s">
-        <v>242</v>
+        <v>433</v>
       </c>
       <c r="H104" s="35" t="n">
         <v>80</v>
       </c>
-      <c r="I104" s="35" t="n">
-        <v>100</v>
-      </c>
-      <c r="J104" s="33"/>
+      <c r="I104" s="33"/>
+      <c r="J104" s="33" t="s">
+        <v>515</v>
+      </c>
       <c r="K104" s="33" t="s">
-        <v>522</v>
-      </c>
-      <c r="L104" s="33" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="36" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="B105" s="36" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="C105" s="36" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="D105" s="36" t="s">
-        <v>524</v>
+        <v>517</v>
       </c>
       <c r="E105" s="34" t="s">
-        <v>525</v>
+        <v>518</v>
       </c>
       <c r="F105" s="33" t="s">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="G105" s="33" t="s">
-        <v>104</v>
+        <v>433</v>
       </c>
       <c r="H105" s="35" t="n">
         <v>120</v>
       </c>
-      <c r="I105" s="35" t="n">
-        <v>134</v>
-      </c>
-      <c r="J105" s="33"/>
+      <c r="I105" s="33"/>
+      <c r="J105" s="33" t="s">
+        <v>519</v>
+      </c>
       <c r="K105" s="33" t="s">
-        <v>526</v>
-      </c>
-      <c r="L105" s="33" t="s">
-        <v>527</v>
+        <v>520</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="36" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="B106" s="36" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="C106" s="36" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="D106" s="36" t="s">
-        <v>528</v>
+        <v>521</v>
       </c>
       <c r="E106" s="34" t="s">
-        <v>529</v>
+        <v>522</v>
       </c>
       <c r="F106" s="33" t="s">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="G106" s="33" t="s">
-        <v>242</v>
+        <v>433</v>
       </c>
       <c r="H106" s="35" t="n">
         <v>140</v>
       </c>
-      <c r="I106" s="35" t="n">
-        <v>150</v>
-      </c>
-      <c r="J106" s="33"/>
+      <c r="I106" s="33"/>
+      <c r="J106" s="33" t="s">
+        <v>523</v>
+      </c>
       <c r="K106" s="33" t="s">
-        <v>530</v>
-      </c>
-      <c r="L106" s="33" t="s">
-        <v>531</v>
+        <v>524</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="36" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="B107" s="36" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="C107" s="36" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="D107" s="36" t="s">
-        <v>532</v>
+        <v>525</v>
       </c>
       <c r="E107" s="34" t="s">
-        <v>533</v>
+        <v>526</v>
       </c>
       <c r="F107" s="33" t="s">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="G107" s="33" t="s">
-        <v>104</v>
+        <v>433</v>
       </c>
       <c r="H107" s="35" t="n">
         <v>150</v>
       </c>
-      <c r="I107" s="35" t="n">
-        <v>230</v>
-      </c>
-      <c r="J107" s="33"/>
+      <c r="I107" s="33"/>
+      <c r="J107" s="33" t="s">
+        <v>527</v>
+      </c>
       <c r="K107" s="33" t="s">
-        <v>534</v>
-      </c>
-      <c r="L107" s="33" t="s">
-        <v>535</v>
+        <v>528</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="36" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="B108" s="36" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="C108" s="36" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="D108" s="36" t="s">
-        <v>536</v>
+        <v>529</v>
       </c>
       <c r="E108" s="34" t="s">
-        <v>537</v>
+        <v>530</v>
       </c>
       <c r="F108" s="33" t="s">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="G108" s="33" t="s">
-        <v>242</v>
+        <v>433</v>
       </c>
       <c r="H108" s="35" t="n">
         <v>170</v>
       </c>
-      <c r="I108" s="35" t="n">
-        <v>260</v>
-      </c>
-      <c r="J108" s="33"/>
+      <c r="I108" s="33"/>
+      <c r="J108" s="33" t="s">
+        <v>531</v>
+      </c>
       <c r="K108" s="33" t="s">
-        <v>538</v>
-      </c>
-      <c r="L108" s="33" t="s">
-        <v>539</v>
+        <v>532</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="36" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="B109" s="36" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="C109" s="36" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="D109" s="36" t="s">
-        <v>540</v>
+        <v>533</v>
       </c>
       <c r="E109" s="34" t="s">
-        <v>541</v>
+        <v>534</v>
       </c>
       <c r="F109" s="33" t="s">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="G109" s="33" t="s">
-        <v>104</v>
+        <v>433</v>
       </c>
       <c r="H109" s="35" t="n">
         <v>150</v>
       </c>
-      <c r="I109" s="35" t="n">
-        <v>160</v>
-      </c>
-      <c r="J109" s="33"/>
+      <c r="I109" s="33"/>
+      <c r="J109" s="33" t="s">
+        <v>535</v>
+      </c>
       <c r="K109" s="33" t="s">
-        <v>542</v>
-      </c>
-      <c r="L109" s="33" t="s">
-        <v>543</v>
+        <v>536</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="36" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="B110" s="36" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="C110" s="36" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="D110" s="36" t="s">
-        <v>544</v>
+        <v>537</v>
       </c>
       <c r="E110" s="34" t="s">
-        <v>545</v>
+        <v>538</v>
       </c>
       <c r="F110" s="33" t="s">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="G110" s="33" t="s">
-        <v>242</v>
+        <v>433</v>
       </c>
       <c r="H110" s="35" t="n">
         <v>170</v>
       </c>
-      <c r="I110" s="35" t="n">
-        <v>180</v>
-      </c>
-      <c r="J110" s="33"/>
+      <c r="I110" s="33"/>
+      <c r="J110" s="33" t="s">
+        <v>539</v>
+      </c>
       <c r="K110" s="33" t="s">
-        <v>546</v>
-      </c>
-      <c r="L110" s="33" t="s">
-        <v>547</v>
+        <v>540</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="36" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="B111" s="36" t="s">
-        <v>548</v>
+        <v>541</v>
       </c>
       <c r="C111" s="36" t="s">
-        <v>548</v>
+        <v>541</v>
       </c>
       <c r="D111" s="36" t="s">
-        <v>549</v>
+        <v>542</v>
       </c>
       <c r="E111" s="34" t="s">
-        <v>550</v>
+        <v>543</v>
       </c>
       <c r="F111" s="33"/>
       <c r="G111" s="33" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="H111" s="35" t="n">
         <v>1.8</v>
       </c>
-      <c r="I111" s="35" t="s">
-        <v>126</v>
-      </c>
-      <c r="J111" s="33"/>
+      <c r="I111" s="33"/>
+      <c r="J111" s="33" t="s">
+        <v>544</v>
+      </c>
       <c r="K111" s="33" t="s">
-        <v>551</v>
-      </c>
-      <c r="L111" s="33" t="s">
-        <v>552</v>
+        <v>545</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="36" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="B112" s="36" t="s">
-        <v>548</v>
+        <v>541</v>
       </c>
       <c r="C112" s="36" t="s">
-        <v>548</v>
+        <v>541</v>
       </c>
       <c r="D112" s="36" t="s">
-        <v>553</v>
+        <v>546</v>
       </c>
       <c r="E112" s="34" t="s">
-        <v>554</v>
+        <v>547</v>
       </c>
       <c r="F112" s="33"/>
       <c r="G112" s="33" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="H112" s="35" t="n">
         <v>1.8</v>
       </c>
-      <c r="I112" s="35" t="s">
-        <v>126</v>
-      </c>
-      <c r="J112" s="33"/>
+      <c r="I112" s="33"/>
+      <c r="J112" s="33" t="s">
+        <v>548</v>
+      </c>
       <c r="K112" s="33" t="s">
-        <v>555</v>
-      </c>
-      <c r="L112" s="33" t="s">
-        <v>556</v>
+        <v>549</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="36" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="B113" s="36" t="s">
-        <v>548</v>
+        <v>541</v>
       </c>
       <c r="C113" s="36" t="s">
-        <v>548</v>
+        <v>541</v>
       </c>
       <c r="D113" s="36" t="s">
-        <v>557</v>
+        <v>550</v>
       </c>
       <c r="E113" s="34" t="s">
-        <v>558</v>
+        <v>551</v>
       </c>
       <c r="F113" s="33"/>
       <c r="G113" s="33" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="H113" s="35" t="n">
         <v>1.8</v>
       </c>
-      <c r="I113" s="35" t="s">
-        <v>126</v>
-      </c>
-      <c r="J113" s="33"/>
+      <c r="I113" s="33"/>
+      <c r="J113" s="33" t="s">
+        <v>552</v>
+      </c>
       <c r="K113" s="33" t="s">
-        <v>559</v>
-      </c>
-      <c r="L113" s="33" t="s">
-        <v>560</v>
+        <v>553</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="36" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="B114" s="36" t="s">
-        <v>548</v>
+        <v>541</v>
       </c>
       <c r="C114" s="36" t="s">
-        <v>548</v>
+        <v>541</v>
       </c>
       <c r="D114" s="36" t="s">
-        <v>561</v>
+        <v>554</v>
       </c>
       <c r="E114" s="34" t="s">
-        <v>562</v>
+        <v>555</v>
       </c>
       <c r="F114" s="33"/>
       <c r="G114" s="33" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="H114" s="35" t="n">
         <v>30</v>
       </c>
-      <c r="I114" s="35" t="s">
-        <v>126</v>
-      </c>
-      <c r="J114" s="33"/>
+      <c r="I114" s="33"/>
+      <c r="J114" s="33" t="s">
+        <v>556</v>
+      </c>
       <c r="K114" s="33" t="s">
-        <v>563</v>
-      </c>
-      <c r="L114" s="33" t="s">
-        <v>564</v>
+        <v>557</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="36" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="B115" s="36" t="s">
-        <v>548</v>
+        <v>541</v>
       </c>
       <c r="C115" s="36" t="s">
-        <v>548</v>
+        <v>541</v>
       </c>
       <c r="D115" s="36" t="s">
-        <v>565</v>
+        <v>558</v>
       </c>
       <c r="E115" s="34" t="s">
-        <v>566</v>
+        <v>559</v>
       </c>
       <c r="F115" s="33"/>
       <c r="G115" s="33" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="H115" s="35" t="n">
         <v>30</v>
       </c>
-      <c r="I115" s="35" t="s">
-        <v>126</v>
-      </c>
-      <c r="J115" s="33"/>
+      <c r="I115" s="33"/>
+      <c r="J115" s="33" t="s">
+        <v>560</v>
+      </c>
       <c r="K115" s="33" t="s">
-        <v>567</v>
-      </c>
-      <c r="L115" s="33" t="s">
-        <v>568</v>
+        <v>561</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="36" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="B116" s="36" t="s">
-        <v>548</v>
+        <v>541</v>
       </c>
       <c r="C116" s="36" t="s">
-        <v>548</v>
+        <v>541</v>
       </c>
       <c r="D116" s="36" t="s">
-        <v>569</v>
+        <v>562</v>
       </c>
       <c r="E116" s="34" t="s">
-        <v>570</v>
+        <v>563</v>
       </c>
       <c r="F116" s="33"/>
       <c r="G116" s="33" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="H116" s="35" t="n">
         <v>30</v>
       </c>
-      <c r="I116" s="35" t="s">
-        <v>126</v>
-      </c>
-      <c r="J116" s="33"/>
+      <c r="I116" s="33"/>
+      <c r="J116" s="33" t="s">
+        <v>564</v>
+      </c>
       <c r="K116" s="33" t="s">
-        <v>571</v>
-      </c>
-      <c r="L116" s="33" t="s">
-        <v>572</v>
+        <v>565</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="36" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="B117" s="36" t="s">
-        <v>548</v>
+        <v>541</v>
       </c>
       <c r="C117" s="36" t="s">
-        <v>548</v>
+        <v>541</v>
       </c>
       <c r="D117" s="36" t="s">
-        <v>573</v>
+        <v>566</v>
       </c>
       <c r="E117" s="34" t="s">
-        <v>574</v>
+        <v>567</v>
       </c>
       <c r="F117" s="33" t="s">
-        <v>575</v>
+        <v>568</v>
       </c>
       <c r="G117" s="33" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="H117" s="35" t="n">
         <v>150</v>
       </c>
-      <c r="I117" s="35" t="s">
-        <v>126</v>
-      </c>
-      <c r="J117" s="33"/>
+      <c r="I117" s="33"/>
+      <c r="J117" s="33" t="s">
+        <v>569</v>
+      </c>
       <c r="K117" s="33" t="s">
-        <v>576</v>
-      </c>
-      <c r="L117" s="33" t="s">
-        <v>577</v>
+        <v>570</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L117"/>
+  <autoFilter ref="A1:K117"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -8235,67 +7834,67 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="16" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C1" s="16" t="s">
-        <v>578</v>
+        <v>571</v>
       </c>
       <c r="D1" s="16" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E1" s="16" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F1" s="16" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="33" t="s">
-        <v>579</v>
+        <v>572</v>
       </c>
       <c r="B2" s="33" t="s">
-        <v>580</v>
+        <v>573</v>
       </c>
       <c r="C2" s="37" t="n">
         <v>1.49061763869132</v>
       </c>
       <c r="D2" s="33" t="s">
-        <v>581</v>
+        <v>574</v>
       </c>
       <c r="E2" s="34" t="s">
-        <v>582</v>
+        <v>575</v>
       </c>
       <c r="F2" s="33" t="s">
-        <v>583</v>
+        <v>576</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="33" t="s">
-        <v>584</v>
+        <v>577</v>
       </c>
       <c r="B3" s="33" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C3" s="37" t="n">
         <v>1.40780554765292</v>
       </c>
       <c r="D3" s="33" t="s">
-        <v>581</v>
+        <v>574</v>
       </c>
       <c r="E3" s="34" t="s">
-        <v>585</v>
+        <v>578</v>
       </c>
       <c r="F3" s="33" t="s">
-        <v>586</v>
+        <v>579</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="38" t="s">
-        <v>587</v>
+        <v>580</v>
       </c>
       <c r="B5" s="38"/>
       <c r="C5" s="38"/>
